--- a/output/daily_ratings/france_ratings_2026-03-17.xlsx
+++ b/output/daily_ratings/france_ratings_2026-03-17.xlsx
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P2" t="n">
-        <v>122.2469253554297</v>
+        <v>120.5898501797769</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.438970000000012</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>92.58707204518741</v>
+        <v>91.27322201459462</v>
       </c>
       <c r="T2" t="n">
-        <v>92.58707204518741</v>
+        <v>91.27322201459462</v>
       </c>
     </row>
     <row r="3">
@@ -650,10 +650,10 @@
         <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P3" t="n">
-        <v>116.0987123226217</v>
+        <v>114.4603948074345</v>
       </c>
       <c r="Q3" t="n">
         <v>7.379509999999982</v>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>94.48868352654371</v>
+        <v>93.04657208903488</v>
       </c>
       <c r="T3" t="n">
-        <v>94.48868352654371</v>
+        <v>93.04657208903488</v>
       </c>
     </row>
     <row r="4">
@@ -724,10 +724,10 @@
         <v>1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P4" t="n">
-        <v>115.5717226340952</v>
+        <v>113.9350129183766</v>
       </c>
       <c r="Q4" t="n">
         <v>6.277199999999993</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>93.32838943148165</v>
+        <v>91.97314661611868</v>
       </c>
       <c r="T4" t="n">
-        <v>93.32838943148165</v>
+        <v>91.97314661611868</v>
       </c>
     </row>
     <row r="5">
@@ -798,10 +798,10 @@
         <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P5" t="n">
-        <v>113.8150903390072</v>
+        <v>112.1837399548502</v>
       </c>
       <c r="Q5" t="n">
         <v>4.072579999999988</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>90.50741200209379</v>
+        <v>89.36432592731073</v>
       </c>
       <c r="T5" t="n">
-        <v>90.50741200209379</v>
+        <v>89.36432592731073</v>
       </c>
     </row>
     <row r="6">
@@ -872,10 +872,10 @@
         <v>3.65</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P6" t="n">
-        <v>109.4235096012872</v>
+        <v>107.8055575460342</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.643590000000017</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>81.88496409739561</v>
+        <v>81.38837787392173</v>
       </c>
       <c r="T6" t="n">
-        <v>81.88496409739561</v>
+        <v>81.38837787392173</v>
       </c>
     </row>
     <row r="7">
@@ -946,10 +946,10 @@
         <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P7" t="n">
-        <v>106.7885611586551</v>
+        <v>105.1786481007446</v>
       </c>
       <c r="Q7" t="n">
         <v>5.174889999999976</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>86.28852177507061</v>
+        <v>85.47157666323976</v>
       </c>
       <c r="T7" t="n">
-        <v>86.28852177507061</v>
+        <v>85.47157666323976</v>
       </c>
     </row>
     <row r="8">
@@ -1020,10 +1020,10 @@
         <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P8" t="n">
-        <v>105.0319288635671</v>
+        <v>103.4273751372182</v>
       </c>
       <c r="Q8" t="n">
         <v>1.867959999999982</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>82.68254218006849</v>
+        <v>82.13580780874723</v>
       </c>
       <c r="T8" t="n">
-        <v>82.68254218006849</v>
+        <v>82.13580780874723</v>
       </c>
     </row>
     <row r="9">
@@ -1094,10 +1094,10 @@
         <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P9" t="n">
-        <v>101.518664273391</v>
+        <v>99.9248292101654</v>
       </c>
       <c r="Q9" t="n">
         <v>-6.950520000000012</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>73.90057865883576</v>
+        <v>74.01037376839314</v>
       </c>
       <c r="T9" t="n">
-        <v>73.90057865883576</v>
+        <v>74.01037376839314</v>
       </c>
     </row>
     <row r="10">
@@ -1168,10 +1168,10 @@
         <v>6.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P10" t="n">
-        <v>100.640348125847</v>
+        <v>99.0491927284022</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.541280000000015</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>76.41510077221309</v>
+        <v>76.34070425241187</v>
       </c>
       <c r="T10" t="n">
-        <v>76.41510077221309</v>
+        <v>76.34070425241187</v>
       </c>
     </row>
     <row r="11">
@@ -1242,10 +1242,10 @@
         <v>6.300000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P11" t="n">
-        <v>100.1133584373206</v>
+        <v>98.52381083934428</v>
       </c>
       <c r="Q11" t="n">
         <v>-4.745900000000006</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>74.46980451153678</v>
+        <v>74.54033061381112</v>
       </c>
       <c r="T11" t="n">
-        <v>74.46980451153678</v>
+        <v>74.54033061381112</v>
       </c>
     </row>
     <row r="12">
@@ -1316,10 +1316,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P12" t="n">
-        <v>89.57356466679246</v>
+        <v>88.0161730581859</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.438970000000012</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>69.31897241942342</v>
+        <v>69.7916289662315</v>
       </c>
       <c r="T12" t="n">
-        <v>69.31897241942342</v>
+        <v>69.7916289662315</v>
       </c>
     </row>
     <row r="13">
@@ -1390,10 +1390,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P13" t="n">
-        <v>88.69524851924845</v>
+        <v>87.1405365764227</v>
       </c>
       <c r="Q13" t="n">
         <v>2.970269999999999</v>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>71.83349453280076</v>
+        <v>72.12195945025023</v>
       </c>
       <c r="T13" t="n">
-        <v>71.83349453280076</v>
+        <v>72.12195945025023</v>
       </c>
     </row>
     <row r="14">
@@ -1464,10 +1464,10 @@
         <v>12.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P14" t="n">
-        <v>78.15545474872029</v>
+        <v>76.63289879526431</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.541280000000015</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>60.40264511577335</v>
+        <v>61.55767247719424</v>
       </c>
       <c r="T14" t="n">
-        <v>60.40264511577335</v>
+        <v>61.55767247719424</v>
       </c>
     </row>
     <row r="15">
@@ -1538,10 +1538,10 @@
         <v>13.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P15" t="n">
-        <v>73.76387401100023</v>
+        <v>72.25471638644831</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.541280000000015</v>
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>57.27521237037496</v>
+        <v>58.67036158359704</v>
       </c>
       <c r="T15" t="n">
-        <v>57.27521237037496</v>
+        <v>58.67036158359704</v>
       </c>
     </row>
     <row r="16">
@@ -1612,10 +1612,10 @@
         <v>20.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P16" t="n">
-        <v>53.03491862529398</v>
+        <v>53.06855909137155</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.643590000000017</v>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P17" t="n">
-        <v>95.81399919387054</v>
+        <v>94.27182544794317</v>
       </c>
       <c r="Q17" t="n">
         <v>0.7656499999999937</v>
@@ -1696,10 +1696,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S17" t="n">
-        <v>78.23124600528199</v>
+        <v>78.05484067299302</v>
       </c>
       <c r="T17" t="n">
-        <v>78.23124600528199</v>
+        <v>78.05484067299302</v>
       </c>
     </row>
     <row r="18">
@@ -1758,10 +1758,10 @@
         <v>0.15</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P18" t="n">
-        <v>95.29836931162072</v>
+        <v>93.75776870738601</v>
       </c>
       <c r="Q18" t="n">
         <v>4.072579999999988</v>
@@ -1770,10 +1770,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S18" t="n">
-        <v>80.21905037729458</v>
+        <v>79.8966765385312</v>
       </c>
       <c r="T18" t="n">
-        <v>80.21905037729458</v>
+        <v>79.8966765385312</v>
       </c>
     </row>
     <row r="19">
@@ -1832,10 +1832,10 @@
         <v>0.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P19" t="n">
-        <v>95.12649268420411</v>
+        <v>93.58641646053361</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.438970000000012</v>
@@ -1844,10 +1844,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S19" t="n">
-        <v>76.17163884094658</v>
+        <v>76.14893283293665</v>
       </c>
       <c r="T19" t="n">
-        <v>76.17163884094658</v>
+        <v>76.14893283293665</v>
       </c>
     </row>
     <row r="20">
@@ -1906,10 +1906,10 @@
         <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P20" t="n">
-        <v>90.82957699878894</v>
+        <v>89.30261028922386</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.541280000000015</v>
@@ -1918,10 +1918,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S20" t="n">
-        <v>72.32661896841434</v>
+        <v>72.59691273795657</v>
       </c>
       <c r="T20" t="n">
-        <v>72.32661896841434</v>
+        <v>72.59691273795657</v>
       </c>
     </row>
     <row r="21">
@@ -1980,10 +1980,10 @@
         <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P21" t="n">
-        <v>86.53266131337375</v>
+        <v>85.0188041179141</v>
       </c>
       <c r="Q21" t="n">
         <v>4.072579999999988</v>
@@ -1992,10 +1992,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S21" t="n">
-        <v>73.97661425518187</v>
+        <v>74.13352980276831</v>
       </c>
       <c r="T21" t="n">
-        <v>73.97661425518187</v>
+        <v>74.13352980276831</v>
       </c>
     </row>
     <row r="22">
@@ -2054,10 +2054,10 @@
         <v>2.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P22" t="n">
-        <v>86.01703143112394</v>
+        <v>84.50474737735694</v>
       </c>
       <c r="Q22" t="n">
         <v>-9.155140000000017</v>
@@ -2066,10 +2066,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S22" t="n">
-        <v>64.18938614298067</v>
+        <v>65.07114318303832</v>
       </c>
       <c r="T22" t="n">
-        <v>64.18938614298067</v>
+        <v>65.07114318303832</v>
       </c>
     </row>
     <row r="23">
@@ -2128,10 +2128,10 @@
         <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P23" t="n">
-        <v>83.43888201987482</v>
+        <v>81.93446367457108</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.155140000000017</v>
@@ -2140,10 +2140,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S23" t="n">
-        <v>62.35337551882986</v>
+        <v>63.37610002546101</v>
       </c>
       <c r="T23" t="n">
-        <v>62.35337551882986</v>
+        <v>63.37610002546101</v>
       </c>
     </row>
     <row r="24">
@@ -2204,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P24" t="n">
-        <v>108.8589025357003</v>
+        <v>102.2747076641523</v>
       </c>
       <c r="Q24" t="n">
         <v>1.867959999999982</v>
@@ -2216,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>85.40789405057073</v>
+        <v>81.37565004442551</v>
       </c>
       <c r="T24" t="n">
-        <v>85.40789405057073</v>
+        <v>81.37565004442551</v>
       </c>
     </row>
     <row r="25">
@@ -2278,10 +2278,10 @@
         <v>1.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P25" t="n">
-        <v>104.7164571205546</v>
+        <v>98.13138057520885</v>
       </c>
       <c r="Q25" t="n">
         <v>1.867959999999982</v>
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>82.45788123944845</v>
+        <v>78.64322084833863</v>
       </c>
       <c r="T25" t="n">
-        <v>82.45788123944845</v>
+        <v>78.64322084833863</v>
       </c>
     </row>
     <row r="26">
@@ -2352,10 +2352,10 @@
         <v>1.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P26" t="n">
-        <v>104.4402940928782</v>
+        <v>97.85515876927929</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.438970000000012</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>79.90620722186421</v>
+        <v>76.28021440487922</v>
       </c>
       <c r="T26" t="n">
-        <v>79.90620722186421</v>
+        <v>76.28021440487922</v>
       </c>
     </row>
     <row r="27">
@@ -2426,10 +2426,10 @@
         <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P27" t="n">
-        <v>97.53621840096876</v>
+        <v>90.9496136210402</v>
       </c>
       <c r="Q27" t="n">
         <v>-1.438970000000012</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>74.98951920332706</v>
+        <v>71.72616574473442</v>
       </c>
       <c r="T27" t="n">
-        <v>74.98951920332706</v>
+        <v>71.72616574473442</v>
       </c>
     </row>
     <row r="28">
@@ -2500,10 +2500,10 @@
         <v>4.199999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P28" t="n">
-        <v>97.26005537329239</v>
+        <v>90.67339181511063</v>
       </c>
       <c r="Q28" t="n">
         <v>1.867959999999982</v>
@@ -2512,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>77.14785817942834</v>
+        <v>73.72484829538226</v>
       </c>
       <c r="T28" t="n">
-        <v>77.14785817942834</v>
+        <v>73.72484829538226</v>
       </c>
     </row>
     <row r="29">
@@ -2574,10 +2574,10 @@
         <v>5.949999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P29" t="n">
-        <v>92.42720238895575</v>
+        <v>85.83951021134328</v>
       </c>
       <c r="Q29" t="n">
         <v>-2.541280000000015</v>
@@ -2586,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>70.56616790399532</v>
+        <v>67.62922157054273</v>
       </c>
       <c r="T29" t="n">
-        <v>70.56616790399532</v>
+        <v>67.62922157054273</v>
       </c>
     </row>
     <row r="30">
@@ -2648,10 +2648,10 @@
         <v>7.199999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P30" t="n">
-        <v>88.97516454300101</v>
+        <v>82.38673763722373</v>
       </c>
       <c r="Q30" t="n">
         <v>-1.438970000000012</v>
@@ -2660,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>68.89282606034099</v>
+        <v>66.07914540615488</v>
       </c>
       <c r="T30" t="n">
-        <v>68.89282606034099</v>
+        <v>66.07914540615488</v>
       </c>
     </row>
     <row r="31">
@@ -2722,10 +2722,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P31" t="n">
-        <v>83.45190398947342</v>
+        <v>76.86230151863246</v>
       </c>
       <c r="Q31" t="n">
         <v>1.867959999999982</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>67.31448214235404</v>
+        <v>64.61675097509267</v>
       </c>
       <c r="T31" t="n">
-        <v>67.31448214235404</v>
+        <v>64.61675097509267</v>
       </c>
     </row>
     <row r="32">
@@ -2796,10 +2796,10 @@
         <v>13.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P32" t="n">
-        <v>71.02456774403635</v>
+        <v>64.43232025180211</v>
       </c>
       <c r="Q32" t="n">
         <v>-1.438970000000012</v>
@@ -2808,10 +2808,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>56.10943721214443</v>
+        <v>54.23861888977843</v>
       </c>
       <c r="T32" t="n">
-        <v>56.10943721214443</v>
+        <v>54.23861888977843</v>
       </c>
     </row>
     <row r="33">
@@ -2872,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P33" t="n">
-        <v>67.33771221119183</v>
+        <v>62.26700856676003</v>
       </c>
       <c r="Q33" t="n">
         <v>-0.3366600000000091</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>54.26887163584412</v>
+        <v>53.53759365634961</v>
       </c>
       <c r="T33" t="n">
-        <v>54.26887163584412</v>
+        <v>53.53759365634961</v>
       </c>
     </row>
     <row r="34">
@@ -2946,10 +2946,10 @@
         <v>1.5</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P34" t="n">
-        <v>64.66054786882917</v>
+        <v>59.60058988347434</v>
       </c>
       <c r="Q34" t="n">
         <v>-2.541280000000015</v>
@@ -2958,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>50.79234390696889</v>
+        <v>50.32525535243058</v>
       </c>
       <c r="T34" t="n">
-        <v>50.79234390696889</v>
+        <v>50.32525535243058</v>
       </c>
     </row>
     <row r="35">
@@ -3020,10 +3020,10 @@
         <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P35" t="n">
-        <v>63.76815975470828</v>
+        <v>58.71178365571245</v>
       </c>
       <c r="Q35" t="n">
         <v>-2.541280000000015</v>
@@ -3032,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>50.15683610775331</v>
+        <v>49.73910802824727</v>
       </c>
       <c r="T35" t="n">
-        <v>50.15683610775331</v>
+        <v>49.73910802824727</v>
       </c>
     </row>
     <row r="36">
@@ -3094,10 +3094,10 @@
         <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P36" t="n">
-        <v>62.42957758352694</v>
+        <v>57.37857431406961</v>
       </c>
       <c r="Q36" t="n">
         <v>-2.541280000000015</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>49.20357440892995</v>
+        <v>48.8598870419723</v>
       </c>
       <c r="T36" t="n">
-        <v>49.20357440892995</v>
+        <v>48.8598870419723</v>
       </c>
     </row>
     <row r="37">
@@ -3168,10 +3168,10 @@
         <v>2.85</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P37" t="n">
-        <v>62.25109996070277</v>
+        <v>57.20081306851723</v>
       </c>
       <c r="Q37" t="n">
         <v>-1.438970000000012</v>
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>49.8614750147011</v>
+        <v>49.46960574282018</v>
       </c>
       <c r="T37" t="n">
-        <v>49.8614750147011</v>
+        <v>49.46960574282018</v>
       </c>
     </row>
     <row r="38">
@@ -3242,10 +3242,10 @@
         <v>3.6</v>
       </c>
       <c r="O38" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P38" t="n">
-        <v>60.91251778952144</v>
+        <v>55.86760372687439</v>
       </c>
       <c r="Q38" t="n">
         <v>-0.3366600000000091</v>
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>49.693215481492</v>
+        <v>49.31733292222975</v>
       </c>
       <c r="T38" t="n">
-        <v>49.693215481492</v>
+        <v>49.31733292222975</v>
       </c>
     </row>
     <row r="39">
@@ -3316,10 +3316,10 @@
         <v>4.35</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P39" t="n">
-        <v>59.5739356183401</v>
+        <v>54.53439438523154</v>
       </c>
       <c r="Q39" t="n">
         <v>-2.541280000000015</v>
@@ -3328,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>47.16994945144013</v>
+        <v>46.98421560458569</v>
       </c>
       <c r="T39" t="n">
-        <v>47.16994945144013</v>
+        <v>46.98421560458569</v>
       </c>
     </row>
     <row r="40">
@@ -3390,10 +3390,10 @@
         <v>4.85</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P40" t="n">
-        <v>58.68154750421922</v>
+        <v>53.64558815746965</v>
       </c>
       <c r="Q40" t="n">
         <v>-1.438970000000012</v>
@@ -3402,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>47.31944381783881</v>
+        <v>47.12501644608693</v>
       </c>
       <c r="T40" t="n">
-        <v>47.31944381783881</v>
+        <v>47.12501644608693</v>
       </c>
     </row>
     <row r="41">
@@ -3464,10 +3464,10 @@
         <v>12.35</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P41" t="n">
-        <v>45.2957257924059</v>
+        <v>40.31349474104124</v>
       </c>
       <c r="Q41" t="n">
         <v>-2.541280000000015</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>37.00182466399097</v>
+        <v>37.60585841765268</v>
       </c>
       <c r="T41" t="n">
-        <v>37.00182466399097</v>
+        <v>37.60585841765268</v>
       </c>
     </row>
     <row r="42">
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P42" t="n">
-        <v>137.8152797638106</v>
+        <v>135.8205578618974</v>
       </c>
       <c r="Q42" t="n">
         <v>-3.643590000000017</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>102.1039597185939</v>
+        <v>99.86362811320892</v>
       </c>
       <c r="T42" t="n">
-        <v>102.1039597185939</v>
+        <v>99.86362811320892</v>
       </c>
     </row>
     <row r="43">
@@ -3614,10 +3614,10 @@
         <v>0.15</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P43" t="n">
-        <v>137.4766242806008</v>
+        <v>135.4827455184412</v>
       </c>
       <c r="Q43" t="n">
         <v>-2.541280000000015</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>102.6477908091777</v>
+        <v>100.3677967854469</v>
       </c>
       <c r="T43" t="n">
-        <v>102.6477908091777</v>
+        <v>100.3677967854469</v>
       </c>
     </row>
     <row r="44">
@@ -3688,10 +3688,10 @@
         <v>0.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P44" t="n">
-        <v>137.250853958461</v>
+        <v>135.2575372894704</v>
       </c>
       <c r="Q44" t="n">
         <v>-2.541280000000015</v>
@@ -3700,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>102.4870100924907</v>
+        <v>100.2192771231492</v>
       </c>
       <c r="T44" t="n">
-        <v>102.4870100924907</v>
+        <v>100.2192771231492</v>
       </c>
     </row>
     <row r="45">
@@ -3762,10 +3762,10 @@
         <v>2.25</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P45" t="n">
-        <v>132.7354475156642</v>
+        <v>130.7533727100542</v>
       </c>
       <c r="Q45" t="n">
         <v>-2.541280000000015</v>
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>99.27139575875155</v>
+        <v>97.2488838771949</v>
       </c>
       <c r="T45" t="n">
-        <v>99.27139575875155</v>
+        <v>97.2488838771949</v>
       </c>
     </row>
     <row r="46">
@@ -3836,10 +3836,10 @@
         <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P46" t="n">
-        <v>132.1710217103146</v>
+        <v>130.1903521376272</v>
       </c>
       <c r="Q46" t="n">
         <v>-2.541280000000015</v>
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>98.86944396703413</v>
+        <v>96.87758472145062</v>
       </c>
       <c r="T46" t="n">
-        <v>98.86944396703413</v>
+        <v>96.87758472145062</v>
       </c>
     </row>
     <row r="47">
@@ -3910,10 +3910,10 @@
         <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P47" t="n">
-        <v>129.9133184889162</v>
+        <v>127.9382698479192</v>
       </c>
       <c r="Q47" t="n">
         <v>4.072579999999988</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>101.9716497938501</v>
+        <v>99.75407709258074</v>
       </c>
       <c r="T47" t="n">
-        <v>101.9716497938501</v>
+        <v>99.75407709258074</v>
       </c>
     </row>
     <row r="48">
@@ -3984,10 +3984,10 @@
         <v>4.25</v>
       </c>
       <c r="O48" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P48" t="n">
-        <v>128.2200410728674</v>
+        <v>126.2492081306381</v>
       </c>
       <c r="Q48" t="n">
         <v>-2.541280000000015</v>
@@ -3996,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>96.05578142501236</v>
+        <v>94.27849063124064</v>
       </c>
       <c r="T48" t="n">
-        <v>96.05578142501236</v>
+        <v>94.27849063124064</v>
       </c>
     </row>
     <row r="49">
@@ -4058,10 +4058,10 @@
         <v>4.28</v>
       </c>
       <c r="O49" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P49" t="n">
-        <v>128.1523099762254</v>
+        <v>126.1816456619469</v>
       </c>
       <c r="Q49" t="n">
         <v>-3.643590000000017</v>
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>95.22254504439201</v>
+        <v>93.50698656686679</v>
       </c>
       <c r="T49" t="n">
-        <v>95.22254504439201</v>
+        <v>93.50698656686679</v>
       </c>
     </row>
     <row r="50">
@@ -4132,10 +4132,10 @@
         <v>5.78</v>
       </c>
       <c r="O50" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P50" t="n">
-        <v>124.7657551441278</v>
+        <v>122.8035222273848</v>
       </c>
       <c r="Q50" t="n">
         <v>-2.541280000000015</v>
@@ -4144,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>93.59583645970186</v>
+        <v>92.00613979808564</v>
       </c>
       <c r="T50" t="n">
-        <v>93.59583645970186</v>
+        <v>92.00613979808564</v>
       </c>
     </row>
     <row r="51">
@@ -4206,10 +4206,10 @@
         <v>8.780000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P51" t="n">
-        <v>117.9926454799326</v>
+        <v>116.0472753582606</v>
       </c>
       <c r="Q51" t="n">
         <v>-0.3366600000000091</v>
@@ -4218,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>90.34241929032157</v>
+        <v>89.00444626052332</v>
       </c>
       <c r="T51" t="n">
-        <v>90.34241929032157</v>
+        <v>89.00444626052332</v>
       </c>
     </row>
     <row r="52">
@@ -4280,10 +4280,10 @@
         <v>11.28</v>
       </c>
       <c r="O52" t="n">
-        <v>0.1749505941233769</v>
+        <v>0.2805563371141229</v>
       </c>
       <c r="P52" t="n">
-        <v>112.3483874264366</v>
+        <v>110.4170696339904</v>
       </c>
       <c r="Q52" t="n">
         <v>1.867959999999982</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>87.89290570437609</v>
+        <v>86.74535103444957</v>
       </c>
       <c r="T52" t="n">
-        <v>87.89290570437609</v>
+        <v>86.74535103444957</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_ratings/france_ratings_2026-03-17.xlsx
+++ b/output/daily_ratings/france_ratings_2026-03-17.xlsx
@@ -546,7 +546,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P2" t="n">
-        <v>120.5898501797769</v>
+        <v>122.7806309440297</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.438970000000012</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>91.27322201459462</v>
+        <v>92.92278798566687</v>
       </c>
       <c r="T2" t="n">
-        <v>91.27322201459462</v>
+        <v>92.92278798566687</v>
       </c>
     </row>
     <row r="3">
@@ -622,7 +622,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -650,10 +650,10 @@
         <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P3" t="n">
-        <v>114.4603948074345</v>
+        <v>116.631027259103</v>
       </c>
       <c r="Q3" t="n">
         <v>7.379509999999982</v>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>93.04657208903488</v>
+        <v>94.73969156691388</v>
       </c>
       <c r="T3" t="n">
-        <v>93.04657208903488</v>
+        <v>94.73969156691388</v>
       </c>
     </row>
     <row r="4">
@@ -696,7 +696,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         <v>1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P4" t="n">
-        <v>113.9350129183766</v>
+        <v>116.1039183718236</v>
       </c>
       <c r="Q4" t="n">
         <v>6.277199999999993</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>91.97314661611868</v>
+        <v>93.63042434650012</v>
       </c>
       <c r="T4" t="n">
-        <v>91.97314661611868</v>
+        <v>93.63042434650012</v>
       </c>
     </row>
     <row r="5">
@@ -770,7 +770,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
         <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P5" t="n">
-        <v>112.1837399548502</v>
+        <v>114.3468887475588</v>
       </c>
       <c r="Q5" t="n">
         <v>4.072579999999988</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>89.36432592731073</v>
+        <v>90.93343335095645</v>
       </c>
       <c r="T5" t="n">
-        <v>89.36432592731073</v>
+        <v>90.93343335095645</v>
       </c>
     </row>
     <row r="6">
@@ -844,7 +844,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -872,10 +872,10 @@
         <v>3.65</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P6" t="n">
-        <v>107.8055575460342</v>
+        <v>109.9543146868969</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.643590000000017</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>81.38837787392173</v>
+        <v>82.690106253344</v>
       </c>
       <c r="T6" t="n">
-        <v>81.38837787392173</v>
+        <v>82.690106253344</v>
       </c>
     </row>
     <row r="7">
@@ -918,7 +918,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P7" t="n">
-        <v>105.1786481007446</v>
+        <v>107.3187702504998</v>
       </c>
       <c r="Q7" t="n">
         <v>5.174889999999976</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>85.47157666323976</v>
+        <v>86.89929260817169</v>
       </c>
       <c r="T7" t="n">
-        <v>85.47157666323976</v>
+        <v>86.89929260817169</v>
       </c>
     </row>
     <row r="8">
@@ -992,7 +992,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P8" t="n">
-        <v>103.4273751372182</v>
+        <v>105.561740626235</v>
       </c>
       <c r="Q8" t="n">
         <v>1.867959999999982</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>82.13580780874723</v>
+        <v>83.45187680825138</v>
       </c>
       <c r="T8" t="n">
-        <v>82.13580780874723</v>
+        <v>83.45187680825138</v>
       </c>
     </row>
     <row r="9">
@@ -1066,7 +1066,7 @@
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
         <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P9" t="n">
-        <v>99.9248292101654</v>
+        <v>102.0476813777055</v>
       </c>
       <c r="Q9" t="n">
         <v>-6.950520000000012</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>74.01037376839314</v>
+        <v>75.05619559965744</v>
       </c>
       <c r="T9" t="n">
-        <v>74.01037376839314</v>
+        <v>75.05619559965744</v>
       </c>
     </row>
     <row r="10">
@@ -1140,7 +1140,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1168,10 +1168,10 @@
         <v>6.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P10" t="n">
-        <v>99.0491927284022</v>
+        <v>101.1691665655731</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.541280000000015</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>76.34070425241187</v>
+        <v>77.45982412376888</v>
       </c>
       <c r="T10" t="n">
-        <v>76.34070425241187</v>
+        <v>77.45982412376888</v>
       </c>
     </row>
     <row r="11">
@@ -1214,7 +1214,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1242,10 +1242,10 @@
         <v>6.300000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P11" t="n">
-        <v>98.52381083934428</v>
+        <v>100.6420576782936</v>
       </c>
       <c r="Q11" t="n">
         <v>-4.745900000000006</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>74.54033061381112</v>
+        <v>75.60013209897846</v>
       </c>
       <c r="T11" t="n">
-        <v>74.54033061381112</v>
+        <v>75.60013209897846</v>
       </c>
     </row>
     <row r="12">
@@ -1288,7 +1288,7 @@
         <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1316,10 +1316,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P12" t="n">
-        <v>88.0161730581859</v>
+        <v>90.09987993270505</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.438970000000012</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>69.7916289662315</v>
+        <v>70.67455819136632</v>
       </c>
       <c r="T12" t="n">
-        <v>69.7916289662315</v>
+        <v>70.67455819136632</v>
       </c>
     </row>
     <row r="13">
@@ -1362,7 +1362,7 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1390,10 +1390,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P13" t="n">
-        <v>87.1405365764227</v>
+        <v>89.22136512057267</v>
       </c>
       <c r="Q13" t="n">
         <v>2.970269999999999</v>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>72.12195945025023</v>
+        <v>73.07818671547777</v>
       </c>
       <c r="T13" t="n">
-        <v>72.12195945025023</v>
+        <v>73.07818671547777</v>
       </c>
     </row>
     <row r="14">
@@ -1436,7 +1436,7 @@
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         <v>12.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P14" t="n">
-        <v>76.63289879526431</v>
+        <v>78.67918737498408</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.541280000000015</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>61.55767247719424</v>
+        <v>62.14921437285236</v>
       </c>
       <c r="T14" t="n">
-        <v>61.55767247719424</v>
+        <v>62.14921437285236</v>
       </c>
     </row>
     <row r="15">
@@ -1510,7 +1510,7 @@
         <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1538,10 +1538,10 @@
         <v>13.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P15" t="n">
-        <v>72.25471638644831</v>
+        <v>74.28661331432218</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.541280000000015</v>
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>58.67036158359704</v>
+        <v>59.15886090587649</v>
       </c>
       <c r="T15" t="n">
-        <v>58.67036158359704</v>
+        <v>59.15886090587649</v>
       </c>
     </row>
     <row r="16">
@@ -1584,7 +1584,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>20.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P16" t="n">
-        <v>53.06855909137155</v>
+        <v>51.10639906798653</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.643590000000017</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P17" t="n">
-        <v>94.27182544794317</v>
+        <v>96.33032986655947</v>
       </c>
       <c r="Q17" t="n">
         <v>0.7656499999999937</v>
@@ -1696,10 +1696,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S17" t="n">
-        <v>78.05484067299302</v>
+        <v>79.18747139341181</v>
       </c>
       <c r="T17" t="n">
-        <v>78.05484067299302</v>
+        <v>79.18747139341181</v>
       </c>
     </row>
     <row r="18">
@@ -1730,7 +1730,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1758,10 +1758,10 @@
         <v>0.15</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P18" t="n">
-        <v>93.75776870738601</v>
+        <v>95.81458335500869</v>
       </c>
       <c r="Q18" t="n">
         <v>4.072579999999988</v>
@@ -1770,10 +1770,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S18" t="n">
-        <v>79.8966765385312</v>
+        <v>81.08763860889462</v>
       </c>
       <c r="T18" t="n">
-        <v>79.8966765385312</v>
+        <v>81.08763860889462</v>
       </c>
     </row>
     <row r="19">
@@ -1804,7 +1804,7 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
         <v>0.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P19" t="n">
-        <v>93.58641646053361</v>
+        <v>95.64266785115842</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.438970000000012</v>
@@ -1844,10 +1844,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S19" t="n">
-        <v>76.14893283293665</v>
+        <v>77.21847885446229</v>
       </c>
       <c r="T19" t="n">
-        <v>76.14893283293665</v>
+        <v>77.21847885446229</v>
       </c>
     </row>
     <row r="20">
@@ -1878,7 +1878,7 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
         <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P20" t="n">
-        <v>89.30261028922386</v>
+        <v>91.34478025490193</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.541280000000015</v>
@@ -1918,10 +1918,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S20" t="n">
-        <v>72.59691273795657</v>
+        <v>73.54216073635935</v>
       </c>
       <c r="T20" t="n">
-        <v>72.59691273795657</v>
+        <v>73.54216073635935</v>
       </c>
     </row>
     <row r="21">
@@ -1952,7 +1952,7 @@
         <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P21" t="n">
-        <v>85.0188041179141</v>
+        <v>87.04689265864543</v>
       </c>
       <c r="Q21" t="n">
         <v>4.072579999999988</v>
@@ -1992,10 +1992,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S21" t="n">
-        <v>74.13352980276831</v>
+        <v>75.11881624889298</v>
       </c>
       <c r="T21" t="n">
-        <v>74.13352980276831</v>
+        <v>75.11881624889298</v>
       </c>
     </row>
     <row r="22">
@@ -2026,7 +2026,7 @@
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2054,10 +2054,10 @@
         <v>2.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P22" t="n">
-        <v>84.50474737735694</v>
+        <v>86.53114614709466</v>
       </c>
       <c r="Q22" t="n">
         <v>-9.155140000000017</v>
@@ -2066,10 +2066,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S22" t="n">
-        <v>65.07114318303832</v>
+        <v>65.76261139872597</v>
       </c>
       <c r="T22" t="n">
-        <v>65.07114318303832</v>
+        <v>65.76261139872597</v>
       </c>
     </row>
     <row r="23">
@@ -2100,7 +2100,7 @@
         <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>5.965163445478406</v>
+        <v>1200</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
         <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P23" t="n">
-        <v>81.93446367457108</v>
+        <v>83.95241358934076</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.155140000000017</v>
@@ -2140,10 +2140,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S23" t="n">
-        <v>63.37610002546101</v>
+        <v>64.0070754104902</v>
       </c>
       <c r="T23" t="n">
-        <v>63.37610002546101</v>
+        <v>64.0070754104902</v>
       </c>
     </row>
     <row r="24">
@@ -2174,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>6.95935735305814</v>
+        <v>1400</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2204,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P24" t="n">
-        <v>102.2747076641523</v>
+        <v>108.0554231435208</v>
       </c>
       <c r="Q24" t="n">
         <v>1.867959999999982</v>
@@ -2216,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>81.37565004442551</v>
+        <v>85.14951287724436</v>
       </c>
       <c r="T24" t="n">
-        <v>81.37565004442551</v>
+        <v>85.14951287724436</v>
       </c>
     </row>
     <row r="25">
@@ -2250,7 +2250,7 @@
         <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>6.95935735305814</v>
+        <v>1400</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2278,10 +2278,10 @@
         <v>1.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P25" t="n">
-        <v>98.13138057520885</v>
+        <v>103.9216673101194</v>
       </c>
       <c r="Q25" t="n">
         <v>1.867959999999982</v>
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>78.64322084833863</v>
+        <v>82.3353563218098</v>
       </c>
       <c r="T25" t="n">
-        <v>78.64322084833863</v>
+        <v>82.3353563218098</v>
       </c>
     </row>
     <row r="26">
@@ -2324,7 +2324,7 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>6.95935735305814</v>
+        <v>1400</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>1.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P26" t="n">
-        <v>97.85515876927929</v>
+        <v>103.6460835878926</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.438970000000012</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>76.28021440487922</v>
+        <v>79.89647147165087</v>
       </c>
       <c r="T26" t="n">
-        <v>76.28021440487922</v>
+        <v>79.89647147165087</v>
       </c>
     </row>
     <row r="27">
@@ -2398,7 +2398,7 @@
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>6.95935735305814</v>
+        <v>1400</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2426,10 +2426,10 @@
         <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P27" t="n">
-        <v>90.9496136210402</v>
+        <v>96.75649053222371</v>
       </c>
       <c r="Q27" t="n">
         <v>-1.438970000000012</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>71.72616574473442</v>
+        <v>75.20621054592661</v>
       </c>
       <c r="T27" t="n">
-        <v>71.72616574473442</v>
+        <v>75.20621054592661</v>
       </c>
     </row>
     <row r="28">
@@ -2472,7 +2472,7 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>6.95935735305814</v>
+        <v>1400</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2500,10 +2500,10 @@
         <v>4.199999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P28" t="n">
-        <v>90.67339181511063</v>
+        <v>96.48090680999695</v>
       </c>
       <c r="Q28" t="n">
         <v>1.867959999999982</v>
@@ -2512,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>73.72484829538226</v>
+        <v>77.26987452202759</v>
       </c>
       <c r="T28" t="n">
-        <v>73.72484829538226</v>
+        <v>77.26987452202759</v>
       </c>
     </row>
     <row r="29">
@@ -2546,7 +2546,7 @@
         <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>6.95935735305814</v>
+        <v>1400</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         <v>5.949999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P29" t="n">
-        <v>85.83951021134328</v>
+        <v>91.65819167102869</v>
       </c>
       <c r="Q29" t="n">
         <v>-2.541280000000015</v>
@@ -2586,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>67.62922157054273</v>
+        <v>70.984992656514</v>
       </c>
       <c r="T29" t="n">
-        <v>67.62922157054273</v>
+        <v>70.984992656514</v>
       </c>
     </row>
     <row r="30">
@@ -2620,7 +2620,7 @@
         <v>7</v>
       </c>
       <c r="G30" t="n">
-        <v>6.95935735305814</v>
+        <v>1400</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         <v>7.199999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P30" t="n">
-        <v>82.38673763722373</v>
+        <v>88.21339514319422</v>
       </c>
       <c r="Q30" t="n">
         <v>-1.438970000000012</v>
@@ -2660,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>66.07914540615488</v>
+        <v>69.39028699802851</v>
       </c>
       <c r="T30" t="n">
-        <v>66.07914540615488</v>
+        <v>69.39028699802851</v>
       </c>
     </row>
     <row r="31">
@@ -2694,7 +2694,7 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>6.95935735305814</v>
+        <v>1400</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P31" t="n">
-        <v>76.86230151863246</v>
+        <v>82.70172069865907</v>
       </c>
       <c r="Q31" t="n">
         <v>1.867959999999982</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>64.61675097509267</v>
+        <v>67.88935267057904</v>
       </c>
       <c r="T31" t="n">
-        <v>64.61675097509267</v>
+        <v>67.88935267057904</v>
       </c>
     </row>
     <row r="32">
@@ -2768,7 +2768,7 @@
         <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>6.95935735305814</v>
+        <v>1400</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2796,10 +2796,10 @@
         <v>13.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P32" t="n">
-        <v>64.43232025180211</v>
+        <v>70.30045319845499</v>
       </c>
       <c r="Q32" t="n">
         <v>-1.438970000000012</v>
@@ -2808,10 +2808,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>54.23861888977843</v>
+        <v>57.1956085911454</v>
       </c>
       <c r="T32" t="n">
-        <v>54.23861888977843</v>
+        <v>57.1956085911454</v>
       </c>
     </row>
     <row r="33">
@@ -2842,7 +2842,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>10.93613298337708</v>
+        <v>2200</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2872,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P33" t="n">
-        <v>62.26700856676003</v>
+        <v>67.6909767478534</v>
       </c>
       <c r="Q33" t="n">
         <v>-0.3366600000000091</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>53.53759365634961</v>
+        <v>56.16956774160602</v>
       </c>
       <c r="T33" t="n">
-        <v>53.53759365634961</v>
+        <v>56.16956774160602</v>
       </c>
     </row>
     <row r="34">
@@ -2918,7 +2918,7 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>10.93613298337708</v>
+        <v>2200</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         <v>1.5</v>
       </c>
       <c r="O34" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P34" t="n">
-        <v>59.60058988347434</v>
+        <v>65.00224444060173</v>
       </c>
       <c r="Q34" t="n">
         <v>-2.541280000000015</v>
@@ -2958,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>50.32525535243058</v>
+        <v>52.83829709367995</v>
       </c>
       <c r="T34" t="n">
-        <v>50.32525535243058</v>
+        <v>52.83829709367995</v>
       </c>
     </row>
     <row r="35">
@@ -2992,7 +2992,7 @@
         <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>10.93613298337708</v>
+        <v>2200</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P35" t="n">
-        <v>58.71178365571245</v>
+        <v>64.1060003381845</v>
       </c>
       <c r="Q35" t="n">
         <v>-2.541280000000015</v>
@@ -3032,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>49.73910802824727</v>
+        <v>52.22815674728903</v>
       </c>
       <c r="T35" t="n">
-        <v>49.73910802824727</v>
+        <v>52.22815674728903</v>
       </c>
     </row>
     <row r="36">
@@ -3066,7 +3066,7 @@
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>10.93613298337708</v>
+        <v>2200</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3094,10 +3094,10 @@
         <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P36" t="n">
-        <v>57.37857431406961</v>
+        <v>62.76163418455867</v>
       </c>
       <c r="Q36" t="n">
         <v>-2.541280000000015</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>48.8598870419723</v>
+        <v>51.31294622770265</v>
       </c>
       <c r="T36" t="n">
-        <v>48.8598870419723</v>
+        <v>51.31294622770265</v>
       </c>
     </row>
     <row r="37">
@@ -3140,7 +3140,7 @@
         <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>10.93613298337708</v>
+        <v>2200</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
         <v>2.85</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P37" t="n">
-        <v>57.20081306851723</v>
+        <v>62.58238536407522</v>
       </c>
       <c r="Q37" t="n">
         <v>-1.438970000000012</v>
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>49.46960574282018</v>
+        <v>51.94134296280112</v>
       </c>
       <c r="T37" t="n">
-        <v>49.46960574282018</v>
+        <v>51.94134296280112</v>
       </c>
     </row>
     <row r="38">
@@ -3214,7 +3214,7 @@
         <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>10.93613298337708</v>
+        <v>2200</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3242,10 +3242,10 @@
         <v>3.6</v>
       </c>
       <c r="O38" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P38" t="n">
-        <v>55.86760372687439</v>
+        <v>61.23801921044939</v>
       </c>
       <c r="Q38" t="n">
         <v>-0.3366600000000091</v>
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>49.31733292222975</v>
+        <v>51.7765572475914</v>
       </c>
       <c r="T38" t="n">
-        <v>49.31733292222975</v>
+        <v>51.7765572475914</v>
       </c>
     </row>
     <row r="39">
@@ -3288,7 +3288,7 @@
         <v>7</v>
       </c>
       <c r="G39" t="n">
-        <v>10.93613298337708</v>
+        <v>2200</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         <v>4.35</v>
       </c>
       <c r="O39" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P39" t="n">
-        <v>54.53439438523154</v>
+        <v>59.89365305682356</v>
       </c>
       <c r="Q39" t="n">
         <v>-2.541280000000015</v>
@@ -3328,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>46.98421560458569</v>
+        <v>49.3604971192517</v>
       </c>
       <c r="T39" t="n">
-        <v>46.98421560458569</v>
+        <v>49.3604971192517</v>
       </c>
     </row>
     <row r="40">
@@ -3362,7 +3362,7 @@
         <v>8</v>
       </c>
       <c r="G40" t="n">
-        <v>10.93613298337708</v>
+        <v>2200</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
         <v>4.85</v>
       </c>
       <c r="O40" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P40" t="n">
-        <v>53.64558815746965</v>
+        <v>58.99740895440633</v>
       </c>
       <c r="Q40" t="n">
         <v>-1.438970000000012</v>
@@ -3402,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>47.12501644608693</v>
+        <v>49.50078157723744</v>
       </c>
       <c r="T40" t="n">
-        <v>47.12501644608693</v>
+        <v>49.50078157723744</v>
       </c>
     </row>
     <row r="41">
@@ -3436,7 +3436,7 @@
         <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>10.93613298337708</v>
+        <v>2200</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3464,10 +3464,10 @@
         <v>12.35</v>
       </c>
       <c r="O41" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P41" t="n">
-        <v>40.31349474104124</v>
+        <v>45.55374741814799</v>
       </c>
       <c r="Q41" t="n">
         <v>-2.541280000000015</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>37.60585841765268</v>
+        <v>39.59825157699698</v>
       </c>
       <c r="T41" t="n">
-        <v>37.60585841765268</v>
+        <v>39.59825157699698</v>
       </c>
     </row>
     <row r="42">
@@ -3510,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>8.947745168217608</v>
+        <v>1800</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P42" t="n">
-        <v>135.8205578618974</v>
+        <v>137.8365996685223</v>
       </c>
       <c r="Q42" t="n">
         <v>-3.643590000000017</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>99.86362811320892</v>
+        <v>101.6716615807114</v>
       </c>
       <c r="T42" t="n">
-        <v>99.86362811320892</v>
+        <v>101.6716615807114</v>
       </c>
     </row>
     <row r="43">
@@ -3586,7 +3586,7 @@
         <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>8.947745168217608</v>
+        <v>1800</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         <v>0.15</v>
       </c>
       <c r="O43" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P43" t="n">
-        <v>135.4827455184412</v>
+        <v>137.5022578933844</v>
       </c>
       <c r="Q43" t="n">
         <v>-2.541280000000015</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>100.3677967854469</v>
+        <v>102.1944749498268</v>
       </c>
       <c r="T43" t="n">
-        <v>100.3677967854469</v>
+        <v>102.1944749498268</v>
       </c>
     </row>
     <row r="44">
@@ -3660,7 +3660,7 @@
         <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>8.947745168217608</v>
+        <v>1800</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3688,10 +3688,10 @@
         <v>0.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P44" t="n">
-        <v>135.2575372894704</v>
+        <v>137.2793633766258</v>
       </c>
       <c r="Q44" t="n">
         <v>-2.541280000000015</v>
@@ -3700,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>100.2192771231492</v>
+        <v>102.042733992986</v>
       </c>
       <c r="T44" t="n">
-        <v>100.2192771231492</v>
+        <v>102.042733992986</v>
       </c>
     </row>
     <row r="45">
@@ -3734,7 +3734,7 @@
         <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>8.947745168217608</v>
+        <v>1800</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         <v>2.25</v>
       </c>
       <c r="O45" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P45" t="n">
-        <v>130.7533727100542</v>
+        <v>132.8214730414536</v>
       </c>
       <c r="Q45" t="n">
         <v>-2.541280000000015</v>
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>97.2488838771949</v>
+        <v>99.00791485616952</v>
       </c>
       <c r="T45" t="n">
-        <v>97.2488838771949</v>
+        <v>99.00791485616952</v>
       </c>
     </row>
     <row r="46">
@@ -3808,7 +3808,7 @@
         <v>5</v>
       </c>
       <c r="G46" t="n">
-        <v>8.947745168217608</v>
+        <v>1800</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3836,10 +3836,10 @@
         <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P46" t="n">
-        <v>130.1903521376272</v>
+        <v>132.2642367495571</v>
       </c>
       <c r="Q46" t="n">
         <v>-2.541280000000015</v>
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>96.87758472145062</v>
+        <v>98.62856246406747</v>
       </c>
       <c r="T46" t="n">
-        <v>96.87758472145062</v>
+        <v>98.62856246406747</v>
       </c>
     </row>
     <row r="47">
@@ -3882,7 +3882,7 @@
         <v>6</v>
       </c>
       <c r="G47" t="n">
-        <v>8.947745168217608</v>
+        <v>1800</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3910,10 +3910,10 @@
         <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P47" t="n">
-        <v>127.9382698479192</v>
+        <v>130.0352915819709</v>
       </c>
       <c r="Q47" t="n">
         <v>4.072579999999988</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>99.75407709258074</v>
+        <v>101.6137017219191</v>
       </c>
       <c r="T47" t="n">
-        <v>99.75407709258074</v>
+        <v>101.6137017219191</v>
       </c>
     </row>
     <row r="48">
@@ -3956,7 +3956,7 @@
         <v>7</v>
       </c>
       <c r="G48" t="n">
-        <v>8.947745168217608</v>
+        <v>1800</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>4.25</v>
       </c>
       <c r="O48" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P48" t="n">
-        <v>126.2492081306381</v>
+        <v>128.3635827062814</v>
       </c>
       <c r="Q48" t="n">
         <v>-2.541280000000015</v>
@@ -3996,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>94.27849063124064</v>
+        <v>95.97309571935303</v>
       </c>
       <c r="T48" t="n">
-        <v>94.27849063124064</v>
+        <v>95.97309571935303</v>
       </c>
     </row>
     <row r="49">
@@ -4030,7 +4030,7 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>8.947745168217608</v>
+        <v>1800</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4058,10 +4058,10 @@
         <v>4.28</v>
       </c>
       <c r="O49" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P49" t="n">
-        <v>126.1816456619469</v>
+        <v>128.2967143512538</v>
       </c>
       <c r="Q49" t="n">
         <v>-3.643590000000017</v>
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>93.50698656686679</v>
+        <v>95.17714862792413</v>
       </c>
       <c r="T49" t="n">
-        <v>93.50698656686679</v>
+        <v>95.17714862792413</v>
       </c>
     </row>
     <row r="50">
@@ -4104,7 +4104,7 @@
         <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>8.947745168217608</v>
+        <v>1800</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4132,10 +4132,10 @@
         <v>5.78</v>
       </c>
       <c r="O50" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P50" t="n">
-        <v>122.8035222273848</v>
+        <v>124.9532965998746</v>
       </c>
       <c r="Q50" t="n">
         <v>-2.541280000000015</v>
@@ -4144,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>92.00613979808564</v>
+        <v>93.65145907968841</v>
       </c>
       <c r="T50" t="n">
-        <v>92.00613979808564</v>
+        <v>93.65145907968841</v>
       </c>
     </row>
     <row r="51">
@@ -4178,7 +4178,7 @@
         <v>10</v>
       </c>
       <c r="G51" t="n">
-        <v>8.947745168217608</v>
+        <v>1800</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4206,10 +4206,10 @@
         <v>8.780000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P51" t="n">
-        <v>116.0472753582606</v>
+        <v>118.2664610971163</v>
       </c>
       <c r="Q51" t="n">
         <v>-0.3366600000000091</v>
@@ -4218,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>89.00444626052332</v>
+        <v>90.60007998321699</v>
       </c>
       <c r="T51" t="n">
-        <v>89.00444626052332</v>
+        <v>90.60007998321699</v>
       </c>
     </row>
     <row r="52">
@@ -4252,7 +4252,7 @@
         <v>11</v>
       </c>
       <c r="G52" t="n">
-        <v>8.947745168217608</v>
+        <v>1800</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         <v>11.28</v>
       </c>
       <c r="O52" t="n">
-        <v>0.2805563371141229</v>
+        <v>0.0008947482860807204</v>
       </c>
       <c r="P52" t="n">
-        <v>110.4170696339904</v>
+        <v>112.694098178151</v>
       </c>
       <c r="Q52" t="n">
         <v>1.867959999999982</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>86.74535103444957</v>
+        <v>88.30740567094968</v>
       </c>
       <c r="T52" t="n">
-        <v>86.74535103444957</v>
+        <v>88.30740567094968</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_ratings/france_ratings_2026-03-17.xlsx
+++ b/output/daily_ratings/france_ratings_2026-03-17.xlsx
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P2" t="n">
-        <v>122.7806309440297</v>
+        <v>111.9013396166527</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.438970000000012</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>92.92278798566687</v>
+        <v>87.35287644876708</v>
       </c>
       <c r="T2" t="n">
-        <v>92.92278798566687</v>
+        <v>87.35287644876708</v>
       </c>
     </row>
     <row r="3">
@@ -650,10 +650,10 @@
         <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P3" t="n">
-        <v>116.631027259103</v>
+        <v>105.7729354330798</v>
       </c>
       <c r="Q3" t="n">
         <v>7.379509999999982</v>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>94.73969156691388</v>
+        <v>89.20325974281717</v>
       </c>
       <c r="T3" t="n">
-        <v>94.73969156691388</v>
+        <v>89.20325974281717</v>
       </c>
     </row>
     <row r="4">
@@ -724,10 +724,10 @@
         <v>1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P4" t="n">
-        <v>116.1039183718236</v>
+        <v>105.2476436459164</v>
       </c>
       <c r="Q4" t="n">
         <v>6.277199999999993</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>93.63042434650012</v>
+        <v>88.08370499348921</v>
       </c>
       <c r="T4" t="n">
-        <v>93.63042434650012</v>
+        <v>88.08370499348921</v>
       </c>
     </row>
     <row r="5">
@@ -798,10 +798,10 @@
         <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P5" t="n">
-        <v>114.3468887475588</v>
+        <v>103.4966710220384</v>
       </c>
       <c r="Q5" t="n">
         <v>4.072579999999988</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>90.93343335095645</v>
+        <v>85.36282907445535</v>
       </c>
       <c r="T5" t="n">
-        <v>90.93343335095645</v>
+        <v>85.36282907445535</v>
       </c>
     </row>
     <row r="6">
@@ -872,10 +872,10 @@
         <v>3.65</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P6" t="n">
-        <v>109.9543146868969</v>
+        <v>99.11923946234339</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.643590000000017</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>82.690106253344</v>
+        <v>77.04417940878157</v>
       </c>
       <c r="T6" t="n">
-        <v>82.690106253344</v>
+        <v>77.04417940878157</v>
       </c>
     </row>
     <row r="7">
@@ -946,10 +946,10 @@
         <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P7" t="n">
-        <v>107.3187702504998</v>
+        <v>96.49278052652639</v>
       </c>
       <c r="Q7" t="n">
         <v>5.174889999999976</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>86.89929260817169</v>
+        <v>81.30339480472107</v>
       </c>
       <c r="T7" t="n">
-        <v>86.89929260817169</v>
+        <v>81.30339480472107</v>
       </c>
     </row>
     <row r="8">
@@ -1020,10 +1020,10 @@
         <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P8" t="n">
-        <v>105.561740626235</v>
+        <v>94.74180790264839</v>
       </c>
       <c r="Q8" t="n">
         <v>1.867959999999982</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>83.45187680825138</v>
+        <v>77.82428895164266</v>
       </c>
       <c r="T8" t="n">
-        <v>83.45187680825138</v>
+        <v>77.82428895164266</v>
       </c>
     </row>
     <row r="9">
@@ -1094,10 +1094,10 @@
         <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P9" t="n">
-        <v>102.0476813777055</v>
+        <v>91.23986265489239</v>
       </c>
       <c r="Q9" t="n">
         <v>-6.950520000000012</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>75.05619559965744</v>
+        <v>69.34961737739667</v>
       </c>
       <c r="T9" t="n">
-        <v>75.05619559965744</v>
+        <v>69.34961737739667</v>
       </c>
     </row>
     <row r="10">
@@ -1168,10 +1168,10 @@
         <v>6.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P10" t="n">
-        <v>101.1691665655731</v>
+        <v>90.36437634295339</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.541280000000015</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>77.45982412376888</v>
+        <v>71.78032908810259</v>
       </c>
       <c r="T10" t="n">
-        <v>77.45982412376888</v>
+        <v>71.78032908810259</v>
       </c>
     </row>
     <row r="11">
@@ -1242,10 +1242,10 @@
         <v>6.300000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P11" t="n">
-        <v>100.6420576782936</v>
+        <v>89.83908455579001</v>
       </c>
       <c r="Q11" t="n">
         <v>-4.745900000000006</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>75.60013209897846</v>
+        <v>69.90254440473005</v>
       </c>
       <c r="T11" t="n">
-        <v>75.60013209897846</v>
+        <v>69.90254440473005</v>
       </c>
     </row>
     <row r="12">
@@ -1316,10 +1316,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P12" t="n">
-        <v>90.09987993270505</v>
+        <v>79.33324881252203</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.438970000000012</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>70.67455819136632</v>
+        <v>64.95073790119551</v>
       </c>
       <c r="T12" t="n">
-        <v>70.67455819136632</v>
+        <v>64.95073790119551</v>
       </c>
     </row>
     <row r="13">
@@ -1390,10 +1390,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P13" t="n">
-        <v>89.22136512057267</v>
+        <v>78.45776250058303</v>
       </c>
       <c r="Q13" t="n">
         <v>2.970269999999999</v>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>73.07818671547777</v>
+        <v>67.38144961190144</v>
       </c>
       <c r="T13" t="n">
-        <v>73.07818671547777</v>
+        <v>67.38144961190144</v>
       </c>
     </row>
     <row r="14">
@@ -1464,10 +1464,10 @@
         <v>12.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P14" t="n">
-        <v>78.67918737498408</v>
+        <v>67.95192675731505</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.541280000000015</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>62.14921437285236</v>
+        <v>56.36380363601034</v>
       </c>
       <c r="T14" t="n">
-        <v>62.14921437285236</v>
+        <v>56.36380363601034</v>
       </c>
     </row>
     <row r="15">
@@ -1538,10 +1538,10 @@
         <v>13.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P15" t="n">
-        <v>74.28661331432218</v>
+        <v>63.57449519762007</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.541280000000015</v>
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>59.15886090587649</v>
+        <v>53.35276350864857</v>
       </c>
       <c r="T15" t="n">
-        <v>59.15886090587649</v>
+        <v>53.35276350864857</v>
       </c>
     </row>
     <row r="16">
@@ -1612,10 +1612,10 @@
         <v>20.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P16" t="n">
-        <v>51.10639906798653</v>
+        <v>40.48415624870005</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.643590000000017</v>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P17" t="n">
-        <v>96.33032986655947</v>
+        <v>85.77504206070468</v>
       </c>
       <c r="Q17" t="n">
         <v>0.7656499999999937</v>
@@ -1696,10 +1696,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S17" t="n">
-        <v>79.18747139341181</v>
+        <v>73.69756712341469</v>
       </c>
       <c r="T17" t="n">
-        <v>79.18747139341181</v>
+        <v>73.69756712341469</v>
       </c>
     </row>
     <row r="18">
@@ -1758,10 +1758,10 @@
         <v>0.15</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P18" t="n">
-        <v>95.81458335500869</v>
+        <v>85.26107347980276</v>
       </c>
       <c r="Q18" t="n">
         <v>4.072579999999988</v>
@@ -1770,10 +1770,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S18" t="n">
-        <v>81.08763860889462</v>
+        <v>75.61872083933106</v>
       </c>
       <c r="T18" t="n">
-        <v>81.08763860889462</v>
+        <v>75.61872083933106</v>
       </c>
     </row>
     <row r="19">
@@ -1832,10 +1832,10 @@
         <v>0.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P19" t="n">
-        <v>95.64266785115842</v>
+        <v>85.08975061950213</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.438970000000012</v>
@@ -1844,10 +1844,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S19" t="n">
-        <v>77.21847885446229</v>
+        <v>71.70972580703575</v>
       </c>
       <c r="T19" t="n">
-        <v>77.21847885446229</v>
+        <v>71.70972580703575</v>
       </c>
     </row>
     <row r="20">
@@ -1906,10 +1906,10 @@
         <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P20" t="n">
-        <v>91.34478025490193</v>
+        <v>80.80667911198614</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.541280000000015</v>
@@ -1918,10 +1918,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S20" t="n">
-        <v>73.54216073635935</v>
+        <v>68.00536182117996</v>
       </c>
       <c r="T20" t="n">
-        <v>73.54216073635935</v>
+        <v>68.00536182117996</v>
       </c>
     </row>
     <row r="21">
@@ -1980,10 +1980,10 @@
         <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P21" t="n">
-        <v>87.04689265864543</v>
+        <v>76.52360760447016</v>
       </c>
       <c r="Q21" t="n">
         <v>4.072579999999988</v>
@@ -1992,10 +1992,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S21" t="n">
-        <v>75.11881624889298</v>
+        <v>69.60860737363616</v>
       </c>
       <c r="T21" t="n">
-        <v>75.11881624889298</v>
+        <v>69.60860737363616</v>
       </c>
     </row>
     <row r="22">
@@ -2054,10 +2054,10 @@
         <v>2.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P22" t="n">
-        <v>86.53114614709466</v>
+        <v>76.00963902356824</v>
       </c>
       <c r="Q22" t="n">
         <v>-9.155140000000017</v>
@@ -2066,10 +2066,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S22" t="n">
-        <v>65.76261139872597</v>
+        <v>60.15631207888398</v>
       </c>
       <c r="T22" t="n">
-        <v>65.76261139872597</v>
+        <v>60.15631207888398</v>
       </c>
     </row>
     <row r="23">
@@ -2128,10 +2128,10 @@
         <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P23" t="n">
-        <v>83.95241358934076</v>
+        <v>73.43979611905866</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.155140000000017</v>
@@ -2140,10 +2140,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S23" t="n">
-        <v>64.0070754104902</v>
+        <v>58.38863164779725</v>
       </c>
       <c r="T23" t="n">
-        <v>64.0070754104902</v>
+        <v>58.38863164779725</v>
       </c>
     </row>
     <row r="24">
@@ -2204,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P24" t="n">
-        <v>108.0554231435208</v>
+        <v>99.84154122160601</v>
       </c>
       <c r="Q24" t="n">
         <v>1.867959999999982</v>
@@ -2216,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>85.14951287724436</v>
+        <v>81.33216827604154</v>
       </c>
       <c r="T24" t="n">
-        <v>85.14951287724436</v>
+        <v>81.33216827604154</v>
       </c>
     </row>
     <row r="25">
@@ -2278,10 +2278,10 @@
         <v>1.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P25" t="n">
-        <v>103.9216673101194</v>
+        <v>95.73050797368786</v>
       </c>
       <c r="Q25" t="n">
         <v>1.867959999999982</v>
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>82.3353563218098</v>
+        <v>78.50437167760369</v>
       </c>
       <c r="T25" t="n">
-        <v>82.3353563218098</v>
+        <v>78.50437167760369</v>
       </c>
     </row>
     <row r="26">
@@ -2352,10 +2352,10 @@
         <v>1.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P26" t="n">
-        <v>103.6460835878926</v>
+        <v>95.45643909049332</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.438970000000012</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>79.89647147165087</v>
+        <v>76.04116210224079</v>
       </c>
       <c r="T26" t="n">
-        <v>79.89647147165087</v>
+        <v>76.04116210224079</v>
       </c>
     </row>
     <row r="27">
@@ -2426,10 +2426,10 @@
         <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P27" t="n">
-        <v>96.75649053222371</v>
+        <v>88.60471701062974</v>
       </c>
       <c r="Q27" t="n">
         <v>-1.438970000000012</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>75.20621054592661</v>
+        <v>71.32816777151108</v>
       </c>
       <c r="T27" t="n">
-        <v>75.20621054592661</v>
+        <v>71.32816777151108</v>
       </c>
     </row>
     <row r="28">
@@ -2500,10 +2500,10 @@
         <v>4.199999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P28" t="n">
-        <v>96.48090680999695</v>
+        <v>88.3306481274352</v>
       </c>
       <c r="Q28" t="n">
         <v>1.867959999999982</v>
@@ -2512,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>77.26987452202759</v>
+        <v>73.41433780041559</v>
       </c>
       <c r="T28" t="n">
-        <v>77.26987452202759</v>
+        <v>73.41433780041559</v>
       </c>
     </row>
     <row r="29">
@@ -2574,10 +2574,10 @@
         <v>5.949999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P29" t="n">
-        <v>91.65819167102869</v>
+        <v>83.5344426715307</v>
       </c>
       <c r="Q29" t="n">
         <v>-2.541280000000015</v>
@@ -2586,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>70.984992656514</v>
+        <v>67.08232203272651</v>
       </c>
       <c r="T29" t="n">
-        <v>70.984992656514</v>
+        <v>67.08232203272651</v>
       </c>
     </row>
     <row r="30">
@@ -2648,10 +2648,10 @@
         <v>7.199999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P30" t="n">
-        <v>88.21339514319422</v>
+        <v>80.10858163159891</v>
       </c>
       <c r="Q30" t="n">
         <v>-1.438970000000012</v>
@@ -2660,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>69.39028699802851</v>
+        <v>65.4840548014062</v>
       </c>
       <c r="T30" t="n">
-        <v>69.39028699802851</v>
+        <v>65.4840548014062</v>
       </c>
     </row>
     <row r="31">
@@ -2722,10 +2722,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P31" t="n">
-        <v>82.70172069865907</v>
+        <v>74.62720396770806</v>
       </c>
       <c r="Q31" t="n">
         <v>1.867959999999982</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>67.88935267057904</v>
+        <v>63.98834913895615</v>
       </c>
       <c r="T31" t="n">
-        <v>67.88935267057904</v>
+        <v>63.98834913895615</v>
       </c>
     </row>
     <row r="32">
@@ -2796,10 +2796,10 @@
         <v>13.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P32" t="n">
-        <v>70.30045319845499</v>
+        <v>62.29410422395362</v>
       </c>
       <c r="Q32" t="n">
         <v>-1.438970000000012</v>
@@ -2808,10 +2808,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>57.1956085911454</v>
+        <v>53.23026954150892</v>
       </c>
       <c r="T32" t="n">
-        <v>57.1956085911454</v>
+        <v>53.23026954150892</v>
       </c>
     </row>
     <row r="33">
@@ -2872,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P33" t="n">
-        <v>67.6909767478534</v>
+        <v>54.05438588891512</v>
       </c>
       <c r="Q33" t="n">
         <v>-0.3366600000000091</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>56.16956774160602</v>
+        <v>48.32076436499288</v>
       </c>
       <c r="T33" t="n">
-        <v>56.16956774160602</v>
+        <v>48.32076436499288</v>
       </c>
     </row>
     <row r="34">
@@ -2946,10 +2946,10 @@
         <v>1.5</v>
       </c>
       <c r="O34" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P34" t="n">
-        <v>65.00224444060173</v>
+        <v>51.39158042068924</v>
       </c>
       <c r="Q34" t="n">
         <v>-2.541280000000015</v>
@@ -2958,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>52.83829709367995</v>
+        <v>44.9726792603129</v>
       </c>
       <c r="T34" t="n">
-        <v>52.83829709367995</v>
+        <v>44.9726792603129</v>
       </c>
     </row>
     <row r="35">
@@ -3020,10 +3020,10 @@
         <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P35" t="n">
-        <v>64.1060003381845</v>
+        <v>50.50397859794728</v>
       </c>
       <c r="Q35" t="n">
         <v>-2.541280000000015</v>
@@ -3032,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>52.22815674728903</v>
+        <v>44.36213751478263</v>
       </c>
       <c r="T35" t="n">
-        <v>52.22815674728903</v>
+        <v>44.36213751478263</v>
       </c>
     </row>
     <row r="36">
@@ -3094,10 +3094,10 @@
         <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P36" t="n">
-        <v>62.76163418455867</v>
+        <v>49.17257586383434</v>
       </c>
       <c r="Q36" t="n">
         <v>-2.541280000000015</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>51.31294622770265</v>
+        <v>43.44632489648722</v>
       </c>
       <c r="T36" t="n">
-        <v>51.31294622770265</v>
+        <v>43.44632489648722</v>
       </c>
     </row>
     <row r="37">
@@ -3168,10 +3168,10 @@
         <v>2.85</v>
       </c>
       <c r="O37" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P37" t="n">
-        <v>62.58238536407522</v>
+        <v>48.99505549928595</v>
       </c>
       <c r="Q37" t="n">
         <v>-1.438970000000012</v>
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>51.94134296280112</v>
+        <v>44.08244648142573</v>
       </c>
       <c r="T37" t="n">
-        <v>51.94134296280112</v>
+        <v>44.08244648142573</v>
       </c>
     </row>
     <row r="38">
@@ -3242,10 +3242,10 @@
         <v>3.6</v>
       </c>
       <c r="O38" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P38" t="n">
-        <v>61.23801921044939</v>
+        <v>47.66365276517301</v>
       </c>
       <c r="Q38" t="n">
         <v>-0.3366600000000091</v>
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>51.7765572475914</v>
+        <v>43.9248637971749</v>
       </c>
       <c r="T38" t="n">
-        <v>51.7765572475914</v>
+        <v>43.9248637971749</v>
       </c>
     </row>
     <row r="39">
@@ -3316,10 +3316,10 @@
         <v>4.35</v>
       </c>
       <c r="O39" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P39" t="n">
-        <v>59.89365305682356</v>
+        <v>46.33225003106007</v>
       </c>
       <c r="Q39" t="n">
         <v>-2.541280000000015</v>
@@ -3328,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>49.3604971192517</v>
+        <v>41.49259131079034</v>
       </c>
       <c r="T39" t="n">
-        <v>49.3604971192517</v>
+        <v>41.49259131079034</v>
       </c>
     </row>
     <row r="40">
@@ -3390,10 +3390,10 @@
         <v>4.85</v>
       </c>
       <c r="O40" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P40" t="n">
-        <v>58.99740895440633</v>
+        <v>45.44464820831811</v>
       </c>
       <c r="Q40" t="n">
         <v>-1.438970000000012</v>
@@ -3402,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>49.50078157723744</v>
+        <v>41.64027949930464</v>
       </c>
       <c r="T40" t="n">
-        <v>49.50078157723744</v>
+        <v>41.64027949930464</v>
       </c>
     </row>
     <row r="41">
@@ -3464,10 +3464,10 @@
         <v>12.35</v>
       </c>
       <c r="O41" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P41" t="n">
-        <v>45.55374741814799</v>
+        <v>32.13062086718871</v>
       </c>
       <c r="Q41" t="n">
         <v>-2.541280000000015</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>39.59825157699698</v>
+        <v>31.72392338230594</v>
       </c>
       <c r="T41" t="n">
-        <v>39.59825157699698</v>
+        <v>31.72392338230594</v>
       </c>
     </row>
     <row r="42">
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P42" t="n">
-        <v>137.8365996685223</v>
+        <v>129.5722142680563</v>
       </c>
       <c r="Q42" t="n">
         <v>-3.643590000000017</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>101.6716615807114</v>
+        <v>97.9914239029771</v>
       </c>
       <c r="T42" t="n">
-        <v>101.6716615807114</v>
+        <v>97.9914239029771</v>
       </c>
     </row>
     <row r="43">
@@ -3614,10 +3614,10 @@
         <v>0.15</v>
       </c>
       <c r="O43" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P43" t="n">
-        <v>137.5022578933844</v>
+        <v>129.2398342751859</v>
       </c>
       <c r="Q43" t="n">
         <v>-2.541280000000015</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>102.1944749498268</v>
+        <v>98.52102444957906</v>
       </c>
       <c r="T43" t="n">
-        <v>102.1944749498268</v>
+        <v>98.52102444957906</v>
       </c>
     </row>
     <row r="44">
@@ -3688,10 +3688,10 @@
         <v>0.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P44" t="n">
-        <v>137.2793633766258</v>
+        <v>129.0182476132723</v>
       </c>
       <c r="Q44" t="n">
         <v>-2.541280000000015</v>
@@ -3700,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>102.042733992986</v>
+        <v>98.36860485795067</v>
       </c>
       <c r="T44" t="n">
-        <v>102.042733992986</v>
+        <v>98.36860485795067</v>
       </c>
     </row>
     <row r="45">
@@ -3762,10 +3762,10 @@
         <v>2.25</v>
       </c>
       <c r="O45" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P45" t="n">
-        <v>132.8214730414536</v>
+        <v>124.5865143750006</v>
       </c>
       <c r="Q45" t="n">
         <v>-2.541280000000015</v>
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>99.00791485616952</v>
+        <v>95.32021302538278</v>
       </c>
       <c r="T45" t="n">
-        <v>99.00791485616952</v>
+        <v>95.32021302538278</v>
       </c>
     </row>
     <row r="46">
@@ -3836,10 +3836,10 @@
         <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P46" t="n">
-        <v>132.2642367495571</v>
+        <v>124.0325477202166</v>
       </c>
       <c r="Q46" t="n">
         <v>-2.541280000000015</v>
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>98.62856246406747</v>
+        <v>94.9391640463118</v>
       </c>
       <c r="T46" t="n">
-        <v>98.62856246406747</v>
+        <v>94.9391640463118</v>
       </c>
     </row>
     <row r="47">
@@ -3910,10 +3910,10 @@
         <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P47" t="n">
-        <v>130.0352915819709</v>
+        <v>121.8166811010807</v>
       </c>
       <c r="Q47" t="n">
         <v>4.072579999999988</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>101.6137017219191</v>
+        <v>97.96434773429526</v>
       </c>
       <c r="T47" t="n">
-        <v>101.6137017219191</v>
+        <v>97.96434773429526</v>
       </c>
     </row>
     <row r="48">
@@ -3984,10 +3984,10 @@
         <v>4.25</v>
       </c>
       <c r="O48" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P48" t="n">
-        <v>128.3635827062814</v>
+        <v>120.1547811367288</v>
       </c>
       <c r="Q48" t="n">
         <v>-2.541280000000015</v>
@@ -3996,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>95.97309571935303</v>
+        <v>92.27182119281487</v>
       </c>
       <c r="T48" t="n">
-        <v>95.97309571935303</v>
+        <v>92.27182119281487</v>
       </c>
     </row>
     <row r="49">
@@ -4058,10 +4058,10 @@
         <v>4.28</v>
       </c>
       <c r="O49" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P49" t="n">
-        <v>128.2967143512538</v>
+        <v>120.0883051381547</v>
       </c>
       <c r="Q49" t="n">
         <v>-3.643590000000017</v>
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>95.17714862792413</v>
+        <v>91.46786538128178</v>
       </c>
       <c r="T49" t="n">
-        <v>95.17714862792413</v>
+        <v>91.46786538128178</v>
       </c>
     </row>
     <row r="50">
@@ -4132,10 +4132,10 @@
         <v>5.78</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P50" t="n">
-        <v>124.9532965998746</v>
+        <v>116.7645052094509</v>
       </c>
       <c r="Q50" t="n">
         <v>-2.541280000000015</v>
@@ -4144,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>93.65145907968841</v>
+        <v>89.93980144090044</v>
       </c>
       <c r="T50" t="n">
-        <v>93.65145907968841</v>
+        <v>89.93980144090044</v>
       </c>
     </row>
     <row r="51">
@@ -4206,10 +4206,10 @@
         <v>8.780000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P51" t="n">
-        <v>118.2664610971163</v>
+        <v>110.1169053520433</v>
       </c>
       <c r="Q51" t="n">
         <v>-0.3366600000000091</v>
@@ -4218,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>90.60007998321699</v>
+        <v>86.88367356013772</v>
       </c>
       <c r="T51" t="n">
-        <v>90.60007998321699</v>
+        <v>86.88367356013772</v>
       </c>
     </row>
     <row r="52">
@@ -4280,10 +4280,10 @@
         <v>11.28</v>
       </c>
       <c r="O52" t="n">
-        <v>0.0008947482860807204</v>
+        <v>0.001606227730426731</v>
       </c>
       <c r="P52" t="n">
-        <v>112.694098178151</v>
+        <v>104.5772388042036</v>
       </c>
       <c r="Q52" t="n">
         <v>1.867959999999982</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>88.30740567094968</v>
+        <v>84.589643637517</v>
       </c>
       <c r="T52" t="n">
-        <v>88.30740567094968</v>
+        <v>84.589643637517</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_ratings/france_ratings_2026-03-17.xlsx
+++ b/output/daily_ratings/france_ratings_2026-03-17.xlsx
@@ -579,7 +579,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P2" t="n">
-        <v>111.9013396166527</v>
+        <v>111.9117717731613</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.438970000000012</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.35287644876708</v>
+        <v>87.36563738109903</v>
       </c>
       <c r="T2" t="n">
-        <v>87.35287644876708</v>
+        <v>87.36563738109903</v>
       </c>
     </row>
     <row r="3">
@@ -653,7 +653,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P3" t="n">
-        <v>105.7729354330798</v>
+        <v>105.783209056721</v>
       </c>
       <c r="Q3" t="n">
         <v>7.379509999999982</v>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>89.20325974281717</v>
+        <v>89.21652528745157</v>
       </c>
       <c r="T3" t="n">
-        <v>89.20325974281717</v>
+        <v>89.21652528745157</v>
       </c>
     </row>
     <row r="4">
@@ -727,7 +727,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P4" t="n">
-        <v>105.2476436459164</v>
+        <v>105.2579036810261</v>
       </c>
       <c r="Q4" t="n">
         <v>6.277199999999993</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>88.08370499348921</v>
+        <v>88.09658987773501</v>
       </c>
       <c r="T4" t="n">
-        <v>88.08370499348921</v>
+        <v>88.09658987773501</v>
       </c>
     </row>
     <row r="5">
@@ -801,7 +801,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P5" t="n">
-        <v>103.4966710220384</v>
+        <v>103.5068857620431</v>
       </c>
       <c r="Q5" t="n">
         <v>4.072579999999988</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.36282907445535</v>
+        <v>85.37478038905572</v>
       </c>
       <c r="T5" t="n">
-        <v>85.36282907445535</v>
+        <v>85.37478038905572</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P6" t="n">
-        <v>99.11923946234339</v>
+        <v>99.12934096458572</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.643590000000017</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>77.04417940878157</v>
+        <v>77.05329385179347</v>
       </c>
       <c r="T6" t="n">
-        <v>77.04417940878157</v>
+        <v>77.05329385179347</v>
       </c>
     </row>
     <row r="7">
@@ -949,7 +949,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P7" t="n">
-        <v>96.49278052652639</v>
+        <v>96.50281408611129</v>
       </c>
       <c r="Q7" t="n">
         <v>5.174889999999976</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>81.30339480472107</v>
+        <v>81.31387510437658</v>
       </c>
       <c r="T7" t="n">
-        <v>81.30339480472107</v>
+        <v>81.31387510437658</v>
       </c>
     </row>
     <row r="8">
@@ -1023,7 +1023,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P8" t="n">
-        <v>94.74180790264839</v>
+        <v>94.75179616712833</v>
       </c>
       <c r="Q8" t="n">
         <v>1.867959999999982</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>77.82428895164266</v>
+        <v>77.83358420791528</v>
       </c>
       <c r="T8" t="n">
-        <v>77.82428895164266</v>
+        <v>77.83358420791528</v>
       </c>
     </row>
     <row r="9">
@@ -1097,7 +1097,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P9" t="n">
-        <v>91.23986265489239</v>
+        <v>91.24976032916243</v>
       </c>
       <c r="Q9" t="n">
         <v>-6.950520000000012</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>69.34961737739667</v>
+        <v>69.3560395994287</v>
       </c>
       <c r="T9" t="n">
-        <v>69.34961737739667</v>
+        <v>69.3560395994287</v>
       </c>
     </row>
     <row r="10">
@@ -1171,7 +1171,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P10" t="n">
-        <v>90.36437634295339</v>
+        <v>90.37425136967094</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.541280000000015</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>71.78032908810259</v>
+        <v>71.78754189399906</v>
       </c>
       <c r="T10" t="n">
-        <v>71.78032908810259</v>
+        <v>71.78754189399906</v>
       </c>
     </row>
     <row r="11">
@@ -1245,7 +1245,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P11" t="n">
-        <v>89.83908455579001</v>
+        <v>89.84894599397606</v>
       </c>
       <c r="Q11" t="n">
         <v>-4.745900000000006</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>69.90254440473005</v>
+        <v>69.90912507650047</v>
       </c>
       <c r="T11" t="n">
-        <v>69.90254440473005</v>
+        <v>69.90912507650047</v>
       </c>
     </row>
     <row r="12">
@@ -1319,7 +1319,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P12" t="n">
-        <v>79.33324881252203</v>
+        <v>79.34283848007831</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.438970000000012</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>64.95073790119551</v>
+        <v>64.9554892611548</v>
       </c>
       <c r="T12" t="n">
-        <v>64.95073790119551</v>
+        <v>64.9554892611548</v>
       </c>
     </row>
     <row r="13">
@@ -1393,7 +1393,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P13" t="n">
-        <v>78.45776250058303</v>
+        <v>78.46732952058684</v>
       </c>
       <c r="Q13" t="n">
         <v>2.970269999999999</v>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>67.38144961190144</v>
+        <v>67.38699155572517</v>
       </c>
       <c r="T13" t="n">
-        <v>67.38144961190144</v>
+        <v>67.38699155572517</v>
       </c>
     </row>
     <row r="14">
@@ -1467,7 +1467,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P14" t="n">
-        <v>67.95192675731505</v>
+        <v>67.9612220066891</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.541280000000015</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>56.36380363601034</v>
+        <v>56.36550447812346</v>
       </c>
       <c r="T14" t="n">
-        <v>56.36380363601034</v>
+        <v>56.36550447812346</v>
       </c>
     </row>
     <row r="15">
@@ -1541,7 +1541,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P15" t="n">
-        <v>63.57449519762007</v>
+        <v>63.58367720923172</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.541280000000015</v>
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>53.35276350864857</v>
+        <v>53.35338779533525</v>
       </c>
       <c r="T15" t="n">
-        <v>53.35276350864857</v>
+        <v>53.35338779533525</v>
       </c>
     </row>
     <row r="16">
@@ -1615,7 +1615,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P16" t="n">
-        <v>40.48415624870005</v>
+        <v>40.49274094696025</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.643590000000017</v>
@@ -1687,7 +1687,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P17" t="n">
-        <v>85.77504206070468</v>
+        <v>85.78458012861385</v>
       </c>
       <c r="Q17" t="n">
         <v>0.7656499999999937</v>
@@ -1696,10 +1696,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S17" t="n">
-        <v>73.69756712341469</v>
+        <v>73.70518394262662</v>
       </c>
       <c r="T17" t="n">
-        <v>73.69756712341469</v>
+        <v>73.70518394262662</v>
       </c>
     </row>
     <row r="18">
@@ -1761,7 +1761,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P18" t="n">
-        <v>85.26107347980276</v>
+        <v>85.27059825209525</v>
       </c>
       <c r="Q18" t="n">
         <v>4.072579999999988</v>
@@ -1770,10 +1770,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S18" t="n">
-        <v>75.61872083933106</v>
+        <v>75.62696567785561</v>
       </c>
       <c r="T18" t="n">
-        <v>75.61872083933106</v>
+        <v>75.62696567785561</v>
       </c>
     </row>
     <row r="19">
@@ -1835,7 +1835,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P19" t="n">
-        <v>85.08975061950213</v>
+        <v>85.09927095992239</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.438970000000012</v>
@@ -1844,10 +1844,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S19" t="n">
-        <v>71.70972580703575</v>
+        <v>71.71667114290661</v>
       </c>
       <c r="T19" t="n">
-        <v>71.70972580703575</v>
+        <v>71.71667114290661</v>
       </c>
     </row>
     <row r="20">
@@ -1909,7 +1909,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P20" t="n">
-        <v>80.80667911198614</v>
+        <v>80.81608865560078</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.541280000000015</v>
@@ -1918,10 +1918,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S20" t="n">
-        <v>68.00536182117996</v>
+        <v>68.01100233414952</v>
       </c>
       <c r="T20" t="n">
-        <v>68.00536182117996</v>
+        <v>68.01100233414952</v>
       </c>
     </row>
     <row r="21">
@@ -1983,7 +1983,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P21" t="n">
-        <v>76.52360760447016</v>
+        <v>76.53290635127915</v>
       </c>
       <c r="Q21" t="n">
         <v>4.072579999999988</v>
@@ -1992,10 +1992,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S21" t="n">
-        <v>69.60860737363616</v>
+        <v>69.61470337986647</v>
       </c>
       <c r="T21" t="n">
-        <v>69.60860737363616</v>
+        <v>69.61470337986647</v>
       </c>
     </row>
     <row r="22">
@@ -2057,7 +2057,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P22" t="n">
-        <v>76.00963902356824</v>
+        <v>76.01892447476055</v>
       </c>
       <c r="Q22" t="n">
         <v>-9.155140000000017</v>
@@ -2066,10 +2066,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S22" t="n">
-        <v>60.15631207888398</v>
+        <v>60.15926399836543</v>
       </c>
       <c r="T22" t="n">
-        <v>60.15631207888398</v>
+        <v>60.15926399836543</v>
       </c>
     </row>
     <row r="23">
@@ -2131,7 +2131,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P23" t="n">
-        <v>73.43979611905866</v>
+        <v>73.44901509216758</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.155140000000017</v>
@@ -2140,10 +2140,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S23" t="n">
-        <v>58.38863164779725</v>
+        <v>58.39095155778038</v>
       </c>
       <c r="T23" t="n">
-        <v>58.38863164779725</v>
+        <v>58.39095155778038</v>
       </c>
     </row>
     <row r="24">
@@ -2207,7 +2207,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P24" t="n">
-        <v>99.84154122160601</v>
+        <v>99.84153010018592</v>
       </c>
       <c r="Q24" t="n">
         <v>1.867959999999982</v>
@@ -2216,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>81.33216827604154</v>
+        <v>81.33574653864018</v>
       </c>
       <c r="T24" t="n">
-        <v>81.33216827604154</v>
+        <v>81.33574653864018</v>
       </c>
     </row>
     <row r="25">
@@ -2281,7 +2281,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P25" t="n">
-        <v>95.73050797368786</v>
+        <v>95.73020831964008</v>
       </c>
       <c r="Q25" t="n">
         <v>1.867959999999982</v>
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>78.50437167760369</v>
+        <v>78.50681354161283</v>
       </c>
       <c r="T25" t="n">
-        <v>78.50437167760369</v>
+        <v>78.50681354161283</v>
       </c>
     </row>
     <row r="26">
@@ -2355,7 +2355,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P26" t="n">
-        <v>95.45643909049332</v>
+        <v>95.45612020093704</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.438970000000012</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>76.04116210224079</v>
+        <v>76.04277378513167</v>
       </c>
       <c r="T26" t="n">
-        <v>76.04116210224079</v>
+        <v>76.04277378513167</v>
       </c>
     </row>
     <row r="27">
@@ -2429,7 +2429,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P27" t="n">
-        <v>88.60471701062974</v>
+        <v>88.60391723336065</v>
       </c>
       <c r="Q27" t="n">
         <v>-1.438970000000012</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>71.32816777151108</v>
+        <v>71.32788545675275</v>
       </c>
       <c r="T27" t="n">
-        <v>71.32816777151108</v>
+        <v>71.32788545675275</v>
       </c>
     </row>
     <row r="28">
@@ -2503,7 +2503,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P28" t="n">
-        <v>88.3306481274352</v>
+        <v>88.32982911465758</v>
       </c>
       <c r="Q28" t="n">
         <v>1.867959999999982</v>
@@ -2512,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>73.41433780041559</v>
+        <v>73.4147341469636</v>
       </c>
       <c r="T28" t="n">
-        <v>73.41433780041559</v>
+        <v>73.4147341469636</v>
       </c>
     </row>
     <row r="29">
@@ -2577,7 +2577,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P29" t="n">
-        <v>83.5344426715307</v>
+        <v>83.53328703735411</v>
       </c>
       <c r="Q29" t="n">
         <v>-2.541280000000015</v>
@@ -2586,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>67.08232203272651</v>
+        <v>67.08038668597034</v>
       </c>
       <c r="T29" t="n">
-        <v>67.08232203272651</v>
+        <v>67.08038668597034</v>
       </c>
     </row>
     <row r="30">
@@ -2651,7 +2651,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P30" t="n">
-        <v>80.10858163159891</v>
+        <v>80.10718555356591</v>
       </c>
       <c r="Q30" t="n">
         <v>-1.438970000000012</v>
@@ -2660,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>65.4840548014062</v>
+        <v>65.48142392956289</v>
       </c>
       <c r="T30" t="n">
-        <v>65.4840548014062</v>
+        <v>65.48142392956289</v>
       </c>
     </row>
     <row r="31">
@@ -2725,7 +2725,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P31" t="n">
-        <v>74.62720396770806</v>
+        <v>74.62542317950481</v>
       </c>
       <c r="Q31" t="n">
         <v>1.867959999999982</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>63.98834913895615</v>
+        <v>63.98495749020577</v>
       </c>
       <c r="T31" t="n">
-        <v>63.98834913895615</v>
+        <v>63.98495749020577</v>
       </c>
     </row>
     <row r="32">
@@ -2799,7 +2799,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P32" t="n">
-        <v>62.29410422395362</v>
+        <v>62.2914578378673</v>
       </c>
       <c r="Q32" t="n">
         <v>-1.438970000000012</v>
@@ -2808,10 +2808,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>53.23026954150892</v>
+        <v>53.22271427577771</v>
       </c>
       <c r="T32" t="n">
-        <v>53.23026954150892</v>
+        <v>53.22271427577771</v>
       </c>
     </row>
     <row r="33">
@@ -2875,7 +2875,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P33" t="n">
-        <v>54.05438588891512</v>
+        <v>54.84175820686502</v>
       </c>
       <c r="Q33" t="n">
         <v>-0.3366600000000091</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>48.32076436499288</v>
+        <v>48.85517971375478</v>
       </c>
       <c r="T33" t="n">
-        <v>48.32076436499288</v>
+        <v>48.85517971375478</v>
       </c>
     </row>
     <row r="34">
@@ -2949,7 +2949,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P34" t="n">
-        <v>51.39158042068924</v>
+        <v>52.17933778072675</v>
       </c>
       <c r="Q34" t="n">
         <v>-2.541280000000015</v>
@@ -2958,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>44.9726792603129</v>
+        <v>45.50624912784947</v>
       </c>
       <c r="T34" t="n">
-        <v>44.9726792603129</v>
+        <v>45.50624912784947</v>
       </c>
     </row>
     <row r="35">
@@ -3023,7 +3023,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P35" t="n">
-        <v>50.50397859794728</v>
+        <v>51.29186430534733</v>
       </c>
       <c r="Q35" t="n">
         <v>-2.541280000000015</v>
@@ -3032,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>44.36213751478263</v>
+        <v>44.89559320440237</v>
       </c>
       <c r="T35" t="n">
-        <v>44.36213751478263</v>
+        <v>44.89559320440237</v>
       </c>
     </row>
     <row r="36">
@@ -3097,7 +3097,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P36" t="n">
-        <v>49.17257586383434</v>
+        <v>49.9606540922782</v>
       </c>
       <c r="Q36" t="n">
         <v>-2.541280000000015</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>43.44632489648722</v>
+        <v>43.97960931923173</v>
       </c>
       <c r="T36" t="n">
-        <v>43.44632489648722</v>
+        <v>43.97960931923173</v>
       </c>
     </row>
     <row r="37">
@@ -3171,7 +3171,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P37" t="n">
-        <v>48.99505549928595</v>
+        <v>49.78315939720232</v>
       </c>
       <c r="Q37" t="n">
         <v>-1.438970000000012</v>
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>44.08244648142573</v>
+        <v>44.61595954232431</v>
       </c>
       <c r="T37" t="n">
-        <v>44.08244648142573</v>
+        <v>44.61595954232431</v>
       </c>
     </row>
     <row r="38">
@@ -3245,7 +3245,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P38" t="n">
-        <v>47.66365276517301</v>
+        <v>48.45194918413318</v>
       </c>
       <c r="Q38" t="n">
         <v>-0.3366600000000091</v>
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>43.9248637971749</v>
+        <v>44.45845706493567</v>
       </c>
       <c r="T38" t="n">
-        <v>43.9248637971749</v>
+        <v>44.45845706493567</v>
       </c>
     </row>
     <row r="39">
@@ -3319,7 +3319,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P39" t="n">
-        <v>46.33225003106007</v>
+        <v>47.12073897106405</v>
       </c>
       <c r="Q39" t="n">
         <v>-2.541280000000015</v>
@@ -3328,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>41.49259131079034</v>
+        <v>42.025510364201</v>
       </c>
       <c r="T39" t="n">
-        <v>41.49259131079034</v>
+        <v>42.025510364201</v>
       </c>
     </row>
     <row r="40">
@@ -3393,7 +3393,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P40" t="n">
-        <v>45.44464820831811</v>
+        <v>46.23326549568463</v>
       </c>
       <c r="Q40" t="n">
         <v>-1.438970000000012</v>
@@ -3402,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>41.64027949930464</v>
+        <v>42.17333584853592</v>
       </c>
       <c r="T40" t="n">
-        <v>41.64027949930464</v>
+        <v>42.17333584853592</v>
       </c>
     </row>
     <row r="41">
@@ -3467,7 +3467,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P41" t="n">
-        <v>32.13062086718871</v>
+        <v>32.9211633649933</v>
       </c>
       <c r="Q41" t="n">
         <v>-2.541280000000015</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>31.72392338230594</v>
+        <v>32.25501558904744</v>
       </c>
       <c r="T41" t="n">
-        <v>31.72392338230594</v>
+        <v>32.25501558904744</v>
       </c>
     </row>
     <row r="42">
@@ -3543,7 +3543,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P42" t="n">
-        <v>129.5722142680563</v>
+        <v>129.7488240674476</v>
       </c>
       <c r="Q42" t="n">
         <v>-3.643590000000017</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>97.9914239029771</v>
+        <v>98.12205731163321</v>
       </c>
       <c r="T42" t="n">
-        <v>97.9914239029771</v>
+        <v>98.12205731163321</v>
       </c>
     </row>
     <row r="43">
@@ -3617,7 +3617,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P43" t="n">
-        <v>129.2398342751859</v>
+        <v>129.416449076701</v>
       </c>
       <c r="Q43" t="n">
         <v>-2.541280000000015</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>98.52102444957906</v>
+        <v>98.65183694687117</v>
       </c>
       <c r="T43" t="n">
-        <v>98.52102444957906</v>
+        <v>98.65183694687117</v>
       </c>
     </row>
     <row r="44">
@@ -3691,7 +3691,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P44" t="n">
-        <v>129.0182476132723</v>
+        <v>129.1948657495366</v>
       </c>
       <c r="Q44" t="n">
         <v>-2.541280000000015</v>
@@ -3700,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>98.36860485795067</v>
+        <v>98.4993690985085</v>
       </c>
       <c r="T44" t="n">
-        <v>98.36860485795067</v>
+        <v>98.4993690985085</v>
       </c>
     </row>
     <row r="45">
@@ -3765,7 +3765,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P45" t="n">
-        <v>124.5865143750006</v>
+        <v>124.7631992062487</v>
       </c>
       <c r="Q45" t="n">
         <v>-2.541280000000015</v>
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>95.32021302538278</v>
+        <v>95.45001213125478</v>
       </c>
       <c r="T45" t="n">
-        <v>95.32021302538278</v>
+        <v>95.45001213125478</v>
       </c>
     </row>
     <row r="46">
@@ -3839,7 +3839,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P46" t="n">
-        <v>124.0325477202166</v>
+        <v>124.2092408883377</v>
       </c>
       <c r="Q46" t="n">
         <v>-2.541280000000015</v>
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>94.9391640463118</v>
+        <v>95.06884251034806</v>
       </c>
       <c r="T46" t="n">
-        <v>94.9391640463118</v>
+        <v>95.06884251034806</v>
       </c>
     </row>
     <row r="47">
@@ -3913,7 +3913,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P47" t="n">
-        <v>121.8166811010807</v>
+        <v>121.9934076166937</v>
       </c>
       <c r="Q47" t="n">
         <v>4.072579999999988</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>97.96434773429526</v>
+        <v>98.09505247341325</v>
       </c>
       <c r="T47" t="n">
-        <v>97.96434773429526</v>
+        <v>98.09505247341325</v>
       </c>
     </row>
     <row r="48">
@@ -3987,7 +3987,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P48" t="n">
-        <v>120.1547811367288</v>
+        <v>120.3315326629607</v>
       </c>
       <c r="Q48" t="n">
         <v>-2.541280000000015</v>
@@ -3996,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>92.27182119281487</v>
+        <v>92.40065516400107</v>
       </c>
       <c r="T48" t="n">
-        <v>92.27182119281487</v>
+        <v>92.40065516400107</v>
       </c>
     </row>
     <row r="49">
@@ -4061,7 +4061,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P49" t="n">
-        <v>120.0883051381547</v>
+        <v>120.2650576648114</v>
       </c>
       <c r="Q49" t="n">
         <v>-3.643590000000017</v>
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>91.46786538128178</v>
+        <v>91.59643340171026</v>
       </c>
       <c r="T49" t="n">
-        <v>91.46786538128178</v>
+        <v>91.59643340171026</v>
       </c>
     </row>
     <row r="50">
@@ -4135,7 +4135,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P50" t="n">
-        <v>116.7645052094509</v>
+        <v>116.9413077573455</v>
       </c>
       <c r="Q50" t="n">
         <v>-2.541280000000015</v>
@@ -4144,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>89.93980144090044</v>
+        <v>90.06789708405198</v>
       </c>
       <c r="T50" t="n">
-        <v>89.93980144090044</v>
+        <v>90.06789708405198</v>
       </c>
     </row>
     <row r="51">
@@ -4209,7 +4209,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P51" t="n">
-        <v>110.1169053520433</v>
+        <v>110.2938079424136</v>
       </c>
       <c r="Q51" t="n">
         <v>-0.3366600000000091</v>
@@ -4218,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>86.88367356013772</v>
+        <v>87.01082444873545</v>
       </c>
       <c r="T51" t="n">
-        <v>86.88367356013772</v>
+        <v>87.01082444873545</v>
       </c>
     </row>
     <row r="52">
@@ -4283,7 +4283,7 @@
         <v>0.001606227730426731</v>
       </c>
       <c r="P52" t="n">
-        <v>104.5772388042036</v>
+        <v>104.7542247633037</v>
       </c>
       <c r="Q52" t="n">
         <v>1.867959999999982</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>84.589643637517</v>
+        <v>84.7160910552323</v>
       </c>
       <c r="T52" t="n">
-        <v>84.589643637517</v>
+        <v>84.7160910552323</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_ratings/france_ratings_2026-03-17.xlsx
+++ b/output/daily_ratings/france_ratings_2026-03-17.xlsx
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P2" t="n">
-        <v>111.9117717731613</v>
+        <v>111.4522913790443</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.438970000000012</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.36563738109903</v>
+        <v>87.91893174103521</v>
       </c>
       <c r="T2" t="n">
-        <v>87.36563738109903</v>
+        <v>87.91893174103521</v>
       </c>
     </row>
     <row r="3">
@@ -650,10 +650,10 @@
         <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P3" t="n">
-        <v>105.783209056721</v>
+        <v>105.3400234181576</v>
       </c>
       <c r="Q3" t="n">
         <v>7.379509999999982</v>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>89.21652528745157</v>
+        <v>89.78555715174124</v>
       </c>
       <c r="T3" t="n">
-        <v>89.21652528745157</v>
+        <v>89.78555715174124</v>
       </c>
     </row>
     <row r="4">
@@ -724,10 +724,10 @@
         <v>1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P4" t="n">
-        <v>105.2579036810261</v>
+        <v>104.8161147357959</v>
       </c>
       <c r="Q4" t="n">
         <v>6.277199999999993</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>88.09658987773501</v>
+        <v>88.66386340713143</v>
       </c>
       <c r="T4" t="n">
-        <v>88.09658987773501</v>
+        <v>88.66386340713143</v>
       </c>
     </row>
     <row r="5">
@@ -798,10 +798,10 @@
         <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P5" t="n">
-        <v>103.5068857620431</v>
+        <v>103.0697524612569</v>
       </c>
       <c r="Q5" t="n">
         <v>4.072579999999988</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.37478038905572</v>
+        <v>85.93865052495087</v>
       </c>
       <c r="T5" t="n">
-        <v>85.37478038905572</v>
+        <v>85.93865052495087</v>
       </c>
     </row>
     <row r="6">
@@ -872,10 +872,10 @@
         <v>3.65</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P6" t="n">
-        <v>99.12934096458572</v>
+        <v>98.70384677490925</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.643590000000017</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>77.05329385179347</v>
+        <v>77.60496891972116</v>
       </c>
       <c r="T6" t="n">
-        <v>77.05329385179347</v>
+        <v>77.60496891972116</v>
       </c>
     </row>
     <row r="7">
@@ -946,10 +946,10 @@
         <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P7" t="n">
-        <v>96.50281408611129</v>
+        <v>96.08430336310067</v>
       </c>
       <c r="Q7" t="n">
         <v>5.174889999999976</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>81.31387510437658</v>
+        <v>81.88072129523147</v>
       </c>
       <c r="T7" t="n">
-        <v>81.31387510437658</v>
+        <v>81.88072129523147</v>
       </c>
     </row>
     <row r="8">
@@ -1020,10 +1020,10 @@
         <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P8" t="n">
-        <v>94.75179616712833</v>
+        <v>94.33794108856164</v>
       </c>
       <c r="Q8" t="n">
         <v>1.867959999999982</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>77.83358420791528</v>
+        <v>78.39518371316174</v>
       </c>
       <c r="T8" t="n">
-        <v>77.83358420791528</v>
+        <v>78.39518371316174</v>
       </c>
     </row>
     <row r="9">
@@ -1094,10 +1094,10 @@
         <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P9" t="n">
-        <v>91.24976032916243</v>
+        <v>90.84521653948353</v>
       </c>
       <c r="Q9" t="n">
         <v>-6.950520000000012</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>69.3560395994287</v>
+        <v>69.9034591492439</v>
       </c>
       <c r="T9" t="n">
-        <v>69.3560395994287</v>
+        <v>69.9034591492439</v>
       </c>
     </row>
     <row r="10">
@@ -1168,10 +1168,10 @@
         <v>6.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P10" t="n">
-        <v>90.37425136967094</v>
+        <v>89.972035402214</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.541280000000015</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>71.78754189399906</v>
+        <v>72.34247620759962</v>
       </c>
       <c r="T10" t="n">
-        <v>71.78754189399906</v>
+        <v>72.34247620759962</v>
       </c>
     </row>
     <row r="11">
@@ -1242,10 +1242,10 @@
         <v>6.300000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P11" t="n">
-        <v>89.84894599397606</v>
+        <v>89.4481267198523</v>
       </c>
       <c r="Q11" t="n">
         <v>-4.745900000000006</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>69.90912507650047</v>
+        <v>70.46045776310058</v>
       </c>
       <c r="T11" t="n">
-        <v>69.90912507650047</v>
+        <v>70.46045776310058</v>
       </c>
     </row>
     <row r="12">
@@ -1316,10 +1316,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P12" t="n">
-        <v>79.34283848007831</v>
+        <v>78.96995307261801</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.438970000000012</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>64.9554892611548</v>
+        <v>65.51405096835529</v>
       </c>
       <c r="T12" t="n">
-        <v>64.9554892611548</v>
+        <v>65.51405096835529</v>
       </c>
     </row>
     <row r="13">
@@ -1390,10 +1390,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P13" t="n">
-        <v>78.46732952058684</v>
+        <v>78.09677193534849</v>
       </c>
       <c r="Q13" t="n">
         <v>2.970269999999999</v>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>67.38699155572517</v>
+        <v>67.95306802671098</v>
       </c>
       <c r="T13" t="n">
-        <v>67.38699155572517</v>
+        <v>67.95306802671098</v>
       </c>
     </row>
     <row r="14">
@@ -1464,10 +1464,10 @@
         <v>12.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P14" t="n">
-        <v>67.9612220066891</v>
+        <v>67.61859828811421</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.541280000000015</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>56.36550447812346</v>
+        <v>56.92406363285215</v>
       </c>
       <c r="T14" t="n">
-        <v>56.36550447812346</v>
+        <v>56.92406363285215</v>
       </c>
     </row>
     <row r="15">
@@ -1538,10 +1538,10 @@
         <v>13.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P15" t="n">
-        <v>63.58367720923172</v>
+        <v>63.25269260176658</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.541280000000015</v>
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>53.35338779533525</v>
+        <v>53.91265492684677</v>
       </c>
       <c r="T15" t="n">
-        <v>53.35338779533525</v>
+        <v>53.91265492684677</v>
       </c>
     </row>
     <row r="16">
@@ -1612,10 +1612,10 @@
         <v>20.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P16" t="n">
-        <v>40.49274094696025</v>
+        <v>40.22301415569359</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.643590000000017</v>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P17" t="n">
-        <v>85.78458012861385</v>
+        <v>85.40378914541644</v>
       </c>
       <c r="Q17" t="n">
         <v>0.7656499999999937</v>
@@ -1696,10 +1696,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S17" t="n">
-        <v>73.70518394262662</v>
+        <v>74.27955659412012</v>
       </c>
       <c r="T17" t="n">
-        <v>73.70518394262662</v>
+        <v>74.27955659412012</v>
       </c>
     </row>
     <row r="18">
@@ -1758,10 +1758,10 @@
         <v>0.15</v>
       </c>
       <c r="O18" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P18" t="n">
-        <v>85.27059825209525</v>
+        <v>84.89117385506566</v>
       </c>
       <c r="Q18" t="n">
         <v>4.072579999999988</v>
@@ -1770,10 +1770,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S18" t="n">
-        <v>75.62696567785561</v>
+        <v>76.20695133154425</v>
       </c>
       <c r="T18" t="n">
-        <v>75.62696567785561</v>
+        <v>76.20695133154425</v>
       </c>
     </row>
     <row r="19">
@@ -1832,10 +1832,10 @@
         <v>0.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P19" t="n">
-        <v>85.09927095992239</v>
+        <v>84.72030209161541</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.438970000000012</v>
@@ -1844,10 +1844,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S19" t="n">
-        <v>71.71667114290661</v>
+        <v>72.28746804468381</v>
       </c>
       <c r="T19" t="n">
-        <v>71.71667114290661</v>
+        <v>72.28746804468381</v>
       </c>
     </row>
     <row r="20">
@@ -1906,10 +1906,10 @@
         <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P20" t="n">
-        <v>80.81608865560078</v>
+        <v>80.44850800535893</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.541280000000015</v>
@@ -1918,10 +1918,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S20" t="n">
-        <v>68.01100233414952</v>
+        <v>68.58064865943261</v>
       </c>
       <c r="T20" t="n">
-        <v>68.01100233414952</v>
+        <v>68.58064865943261</v>
       </c>
     </row>
     <row r="21">
@@ -1980,10 +1980,10 @@
         <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P21" t="n">
-        <v>76.53290635127915</v>
+        <v>76.17671391910247</v>
       </c>
       <c r="Q21" t="n">
         <v>4.072579999999988</v>
@@ -1992,10 +1992,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S21" t="n">
-        <v>69.61470337986647</v>
+        <v>70.19610217340579</v>
       </c>
       <c r="T21" t="n">
-        <v>69.61470337986647</v>
+        <v>70.19610217340579</v>
       </c>
     </row>
     <row r="22">
@@ -2054,10 +2054,10 @@
         <v>2.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P22" t="n">
-        <v>76.01892447476055</v>
+        <v>75.66409862875169</v>
       </c>
       <c r="Q22" t="n">
         <v>-9.155140000000017</v>
@@ -2066,10 +2066,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S22" t="n">
-        <v>60.15926399836543</v>
+        <v>60.71862641249203</v>
       </c>
       <c r="T22" t="n">
-        <v>60.15926399836543</v>
+        <v>60.71862641249203</v>
       </c>
     </row>
     <row r="23">
@@ -2128,10 +2128,10 @@
         <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P23" t="n">
-        <v>73.44901509216758</v>
+        <v>73.1010221769978</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.155140000000017</v>
@@ -2140,10 +2140,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S23" t="n">
-        <v>58.39095155778038</v>
+        <v>58.95072960127483</v>
       </c>
       <c r="T23" t="n">
-        <v>58.39095155778038</v>
+        <v>58.95072960127483</v>
       </c>
     </row>
     <row r="24">
@@ -2204,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P24" t="n">
-        <v>99.84153010018592</v>
+        <v>98.81027047064482</v>
       </c>
       <c r="Q24" t="n">
         <v>1.867959999999982</v>
@@ -2216,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>81.33574653864018</v>
+        <v>81.47999877901259</v>
       </c>
       <c r="T24" t="n">
-        <v>81.33574653864018</v>
+        <v>81.47999877901259</v>
       </c>
     </row>
     <row r="25">
@@ -2278,10 +2278,10 @@
         <v>1.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P25" t="n">
-        <v>95.73020831964008</v>
+        <v>94.71178519066345</v>
       </c>
       <c r="Q25" t="n">
         <v>1.867959999999982</v>
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>78.50681354161283</v>
+        <v>78.65304484545294</v>
       </c>
       <c r="T25" t="n">
-        <v>78.50681354161283</v>
+        <v>78.65304484545294</v>
       </c>
     </row>
     <row r="26">
@@ -2352,10 +2352,10 @@
         <v>1.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P26" t="n">
-        <v>95.45612020093704</v>
+        <v>94.43855283866469</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.438970000000012</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>76.04277378513167</v>
+        <v>76.18360715021473</v>
       </c>
       <c r="T26" t="n">
-        <v>76.04277378513167</v>
+        <v>76.18360715021473</v>
       </c>
     </row>
     <row r="27">
@@ -2426,10 +2426,10 @@
         <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P27" t="n">
-        <v>88.60391723336065</v>
+        <v>87.60774403869573</v>
       </c>
       <c r="Q27" t="n">
         <v>-1.438970000000012</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>71.32788545675275</v>
+        <v>71.47201726094868</v>
       </c>
       <c r="T27" t="n">
-        <v>71.32788545675275</v>
+        <v>71.47201726094868</v>
       </c>
     </row>
     <row r="28">
@@ -2500,10 +2500,10 @@
         <v>4.199999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P28" t="n">
-        <v>88.32982911465758</v>
+        <v>87.33451168669697</v>
       </c>
       <c r="Q28" t="n">
         <v>1.867959999999982</v>
@@ -2512,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>73.4147341469636</v>
+        <v>73.56452776504561</v>
       </c>
       <c r="T28" t="n">
-        <v>73.4147341469636</v>
+        <v>73.56452776504561</v>
       </c>
     </row>
     <row r="29">
@@ -2574,10 +2574,10 @@
         <v>5.949999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P29" t="n">
-        <v>83.53328703735411</v>
+        <v>82.55294552671869</v>
       </c>
       <c r="Q29" t="n">
         <v>-2.541280000000015</v>
@@ -2586,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>67.08038668597034</v>
+        <v>67.2251160430026</v>
       </c>
       <c r="T29" t="n">
-        <v>67.08038668597034</v>
+        <v>67.2251160430026</v>
       </c>
     </row>
     <row r="30">
@@ -2648,10 +2648,10 @@
         <v>7.199999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P30" t="n">
-        <v>80.10718555356591</v>
+        <v>79.13754112673421</v>
       </c>
       <c r="Q30" t="n">
         <v>-1.438970000000012</v>
@@ -2660,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>65.48142392956289</v>
+        <v>65.62964579825876</v>
       </c>
       <c r="T30" t="n">
-        <v>65.48142392956289</v>
+        <v>65.62964579825876</v>
       </c>
     </row>
     <row r="31">
@@ -2722,10 +2722,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P31" t="n">
-        <v>74.62542317950481</v>
+        <v>73.67289408675903</v>
       </c>
       <c r="Q31" t="n">
         <v>1.867959999999982</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>63.98495749020577</v>
+        <v>64.14134798651351</v>
       </c>
       <c r="T31" t="n">
-        <v>63.98495749020577</v>
+        <v>64.14134798651351</v>
       </c>
     </row>
     <row r="32">
@@ -2796,10 +2796,10 @@
         <v>13.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P32" t="n">
-        <v>62.2914578378673</v>
+        <v>61.3774382468149</v>
       </c>
       <c r="Q32" t="n">
         <v>-1.438970000000012</v>
@@ -2808,10 +2808,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>53.22271427577771</v>
+        <v>53.37951208616703</v>
       </c>
       <c r="T32" t="n">
-        <v>53.22271427577771</v>
+        <v>53.37951208616703</v>
       </c>
     </row>
     <row r="33">
@@ -2872,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P33" t="n">
-        <v>54.84175820686502</v>
+        <v>54.10011722542837</v>
       </c>
       <c r="Q33" t="n">
         <v>-0.3366600000000091</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>48.85517971375478</v>
+        <v>49.12026250878121</v>
       </c>
       <c r="T33" t="n">
-        <v>48.85517971375478</v>
+        <v>49.12026250878121</v>
       </c>
     </row>
     <row r="34">
@@ -2946,10 +2946,10 @@
         <v>1.5</v>
       </c>
       <c r="O34" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P34" t="n">
-        <v>52.17933778072675</v>
+        <v>51.44462755407096</v>
       </c>
       <c r="Q34" t="n">
         <v>-2.541280000000015</v>
@@ -2958,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>45.50624912784947</v>
+        <v>45.76797374490953</v>
       </c>
       <c r="T34" t="n">
-        <v>45.50624912784947</v>
+        <v>45.76797374490953</v>
       </c>
     </row>
     <row r="35">
@@ -3020,10 +3020,10 @@
         <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P35" t="n">
-        <v>51.29186430534733</v>
+        <v>50.55946433028516</v>
       </c>
       <c r="Q35" t="n">
         <v>-2.541280000000015</v>
@@ -3032,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>44.89559320440237</v>
+        <v>45.15742729021176</v>
       </c>
       <c r="T35" t="n">
-        <v>44.89559320440237</v>
+        <v>45.15742729021176</v>
       </c>
     </row>
     <row r="36">
@@ -3094,10 +3094,10 @@
         <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P36" t="n">
-        <v>49.9606540922782</v>
+        <v>49.23171949460645</v>
       </c>
       <c r="Q36" t="n">
         <v>-2.541280000000015</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>43.97960931923173</v>
+        <v>44.24160760816512</v>
       </c>
       <c r="T36" t="n">
-        <v>43.97960931923173</v>
+        <v>44.24160760816512</v>
       </c>
     </row>
     <row r="37">
@@ -3168,10 +3168,10 @@
         <v>2.85</v>
       </c>
       <c r="O37" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P37" t="n">
-        <v>49.78315939720232</v>
+        <v>49.05468684984929</v>
       </c>
       <c r="Q37" t="n">
         <v>-1.438970000000012</v>
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>44.61595954232431</v>
+        <v>44.87982301711476</v>
       </c>
       <c r="T37" t="n">
-        <v>44.61595954232431</v>
+        <v>44.87982301711476</v>
       </c>
     </row>
     <row r="38">
@@ -3242,10 +3242,10 @@
         <v>3.6</v>
       </c>
       <c r="O38" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P38" t="n">
-        <v>48.45194918413318</v>
+        <v>47.72694201417058</v>
       </c>
       <c r="Q38" t="n">
         <v>-0.3366600000000091</v>
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>44.45845706493567</v>
+        <v>44.7243280349573</v>
       </c>
       <c r="T38" t="n">
-        <v>44.45845706493567</v>
+        <v>44.7243280349573</v>
       </c>
     </row>
     <row r="39">
@@ -3316,10 +3316,10 @@
         <v>4.35</v>
       </c>
       <c r="O39" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P39" t="n">
-        <v>47.12073897106405</v>
+        <v>46.39919717849188</v>
       </c>
       <c r="Q39" t="n">
         <v>-2.541280000000015</v>
@@ -3328,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>42.025510364201</v>
+        <v>42.28785895313227</v>
       </c>
       <c r="T39" t="n">
-        <v>42.025510364201</v>
+        <v>42.28785895313227</v>
       </c>
     </row>
     <row r="40">
@@ -3390,10 +3390,10 @@
         <v>4.85</v>
       </c>
       <c r="O40" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P40" t="n">
-        <v>46.23326549568463</v>
+        <v>45.51403395470608</v>
       </c>
       <c r="Q40" t="n">
         <v>-1.438970000000012</v>
@@ -3402,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>42.17333584853592</v>
+        <v>42.43763719832371</v>
       </c>
       <c r="T40" t="n">
-        <v>42.17333584853592</v>
+        <v>42.43763719832371</v>
       </c>
     </row>
     <row r="41">
@@ -3464,10 +3464,10 @@
         <v>12.35</v>
       </c>
       <c r="O41" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P41" t="n">
-        <v>32.9211633649933</v>
+        <v>32.23658559791902</v>
       </c>
       <c r="Q41" t="n">
         <v>-2.541280000000015</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>32.25501558904744</v>
+        <v>32.51911567796805</v>
       </c>
       <c r="T41" t="n">
-        <v>32.25501558904744</v>
+        <v>32.51911567796805</v>
       </c>
     </row>
     <row r="42">
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P42" t="n">
-        <v>129.7488240674476</v>
+        <v>128.2623500880567</v>
       </c>
       <c r="Q42" t="n">
         <v>-3.643590000000017</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>98.12205731163321</v>
+        <v>97.99311759000679</v>
       </c>
       <c r="T42" t="n">
-        <v>98.12205731163321</v>
+        <v>97.99311759000679</v>
       </c>
     </row>
     <row r="43">
@@ -3614,10 +3614,10 @@
         <v>0.15</v>
       </c>
       <c r="O43" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P43" t="n">
-        <v>129.416449076701</v>
+        <v>127.9308878428104</v>
       </c>
       <c r="Q43" t="n">
         <v>-2.541280000000015</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>98.65183694687117</v>
+        <v>98.52481428857013</v>
       </c>
       <c r="T43" t="n">
-        <v>98.65183694687117</v>
+        <v>98.52481428857013</v>
       </c>
     </row>
     <row r="44">
@@ -3688,10 +3688,10 @@
         <v>0.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P44" t="n">
-        <v>129.1948657495366</v>
+        <v>127.7099130126462</v>
       </c>
       <c r="Q44" t="n">
         <v>-2.541280000000015</v>
@@ -3700,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>98.4993690985085</v>
+        <v>98.37239562101954</v>
       </c>
       <c r="T44" t="n">
-        <v>98.4993690985085</v>
+        <v>98.37239562101954</v>
       </c>
     </row>
     <row r="45">
@@ -3762,10 +3762,10 @@
         <v>2.25</v>
       </c>
       <c r="O45" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P45" t="n">
-        <v>124.7631992062487</v>
+        <v>123.2904164093617</v>
       </c>
       <c r="Q45" t="n">
         <v>-2.541280000000015</v>
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>95.45001213125478</v>
+        <v>95.32402227000799</v>
       </c>
       <c r="T45" t="n">
-        <v>95.45001213125478</v>
+        <v>95.32402227000799</v>
       </c>
     </row>
     <row r="46">
@@ -3836,10 +3836,10 @@
         <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P46" t="n">
-        <v>124.2092408883377</v>
+        <v>122.7379793339511</v>
       </c>
       <c r="Q46" t="n">
         <v>-2.541280000000015</v>
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>95.06884251034806</v>
+        <v>94.94297560113154</v>
       </c>
       <c r="T46" t="n">
-        <v>95.06884251034806</v>
+        <v>94.94297560113154</v>
       </c>
     </row>
     <row r="47">
@@ -3910,10 +3910,10 @@
         <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P47" t="n">
-        <v>121.9934076166937</v>
+        <v>120.5282310323089</v>
       </c>
       <c r="Q47" t="n">
         <v>4.072579999999988</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>98.09505247341325</v>
+        <v>97.98073712496091</v>
       </c>
       <c r="T47" t="n">
-        <v>98.09505247341325</v>
+        <v>97.98073712496091</v>
       </c>
     </row>
     <row r="48">
@@ -3984,10 +3984,10 @@
         <v>4.25</v>
       </c>
       <c r="O48" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P48" t="n">
-        <v>120.3315326629607</v>
+        <v>118.8709198060772</v>
       </c>
       <c r="Q48" t="n">
         <v>-2.541280000000015</v>
@@ -3996,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>92.40065516400107</v>
+        <v>92.27564891899641</v>
       </c>
       <c r="T48" t="n">
-        <v>92.40065516400107</v>
+        <v>92.27564891899641</v>
       </c>
     </row>
     <row r="49">
@@ -4058,10 +4058,10 @@
         <v>4.28</v>
       </c>
       <c r="O49" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P49" t="n">
-        <v>120.2650576648114</v>
+        <v>118.804627357028</v>
       </c>
       <c r="Q49" t="n">
         <v>-3.643590000000017</v>
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>91.59643340171026</v>
+        <v>91.46959861884204</v>
       </c>
       <c r="T49" t="n">
-        <v>91.59643340171026</v>
+        <v>91.46959861884204</v>
       </c>
     </row>
     <row r="50">
@@ -4132,10 +4132,10 @@
         <v>5.78</v>
       </c>
       <c r="O50" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P50" t="n">
-        <v>116.9413077573455</v>
+        <v>115.4900049045646</v>
       </c>
       <c r="Q50" t="n">
         <v>-2.541280000000015</v>
@@ -4144,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>90.06789708405198</v>
+        <v>89.94364330547256</v>
       </c>
       <c r="T50" t="n">
-        <v>90.06789708405198</v>
+        <v>89.94364330547256</v>
       </c>
     </row>
     <row r="51">
@@ -4206,10 +4206,10 @@
         <v>8.780000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P51" t="n">
-        <v>110.2938079424136</v>
+        <v>108.8607599996379</v>
       </c>
       <c r="Q51" t="n">
         <v>-0.3366600000000091</v>
@@ -4218,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>87.01082444873545</v>
+        <v>86.8917326787336</v>
       </c>
       <c r="T51" t="n">
-        <v>87.01082444873545</v>
+        <v>86.8917326787336</v>
       </c>
     </row>
     <row r="52">
@@ -4280,10 +4280,10 @@
         <v>11.28</v>
       </c>
       <c r="O52" t="n">
-        <v>0.001606227730426731</v>
+        <v>0.001596431204997816</v>
       </c>
       <c r="P52" t="n">
-        <v>104.7542247633037</v>
+        <v>103.3363892455324</v>
       </c>
       <c r="Q52" t="n">
         <v>1.867959999999982</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>84.7160910552323</v>
+        <v>84.60191538974752</v>
       </c>
       <c r="T52" t="n">
-        <v>84.7160910552323</v>
+        <v>84.60191538974752</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_ratings/france_ratings_2026-03-17.xlsx
+++ b/output/daily_ratings/france_ratings_2026-03-17.xlsx
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P2" t="n">
-        <v>111.4522913790443</v>
+        <v>105.7261456895222</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.438970000000012</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.91893174103521</v>
+        <v>83.80438722968697</v>
       </c>
       <c r="T2" t="n">
-        <v>87.91893174103521</v>
+        <v>83.80438722968697</v>
       </c>
     </row>
     <row r="3">
@@ -650,10 +650,10 @@
         <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P3" t="n">
-        <v>105.3400234181576</v>
+        <v>99.61387772863549</v>
       </c>
       <c r="Q3" t="n">
         <v>7.379509999999982</v>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>89.78555715174124</v>
+        <v>85.671012640393</v>
       </c>
       <c r="T3" t="n">
-        <v>89.78555715174124</v>
+        <v>85.671012640393</v>
       </c>
     </row>
     <row r="4">
@@ -724,10 +724,10 @@
         <v>1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P4" t="n">
-        <v>104.8161147357959</v>
+        <v>99.08996904627378</v>
       </c>
       <c r="Q4" t="n">
         <v>6.277199999999993</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>88.66386340713143</v>
+        <v>84.54931889578316</v>
       </c>
       <c r="T4" t="n">
-        <v>88.66386340713143</v>
+        <v>84.54931889578316</v>
       </c>
     </row>
     <row r="5">
@@ -798,10 +798,10 @@
         <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P5" t="n">
-        <v>103.0697524612569</v>
+        <v>97.34360677173473</v>
       </c>
       <c r="Q5" t="n">
         <v>4.072579999999988</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.93865052495087</v>
+        <v>81.82410601360263</v>
       </c>
       <c r="T5" t="n">
-        <v>85.93865052495087</v>
+        <v>81.82410601360263</v>
       </c>
     </row>
     <row r="6">
@@ -872,10 +872,10 @@
         <v>3.65</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P6" t="n">
-        <v>98.70384677490925</v>
+        <v>92.97770108538711</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.643590000000017</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>77.60496891972116</v>
+        <v>73.49042440837292</v>
       </c>
       <c r="T6" t="n">
-        <v>77.60496891972116</v>
+        <v>73.49042440837292</v>
       </c>
     </row>
     <row r="7">
@@ -946,10 +946,10 @@
         <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P7" t="n">
-        <v>96.08430336310067</v>
+        <v>90.35815767357853</v>
       </c>
       <c r="Q7" t="n">
         <v>5.174889999999976</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>81.88072129523147</v>
+        <v>77.76617678388322</v>
       </c>
       <c r="T7" t="n">
-        <v>81.88072129523147</v>
+        <v>77.76617678388322</v>
       </c>
     </row>
     <row r="8">
@@ -1020,10 +1020,10 @@
         <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P8" t="n">
-        <v>94.33794108856164</v>
+        <v>88.61179539903949</v>
       </c>
       <c r="Q8" t="n">
         <v>1.867959999999982</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>78.39518371316174</v>
+        <v>74.28063920181351</v>
       </c>
       <c r="T8" t="n">
-        <v>78.39518371316174</v>
+        <v>74.28063920181351</v>
       </c>
     </row>
     <row r="9">
@@ -1094,10 +1094,10 @@
         <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P9" t="n">
-        <v>90.84521653948353</v>
+        <v>85.11907084996139</v>
       </c>
       <c r="Q9" t="n">
         <v>-6.950520000000012</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>69.9034591492439</v>
+        <v>65.78891463789566</v>
       </c>
       <c r="T9" t="n">
-        <v>69.9034591492439</v>
+        <v>65.78891463789566</v>
       </c>
     </row>
     <row r="10">
@@ -1168,10 +1168,10 @@
         <v>6.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P10" t="n">
-        <v>89.972035402214</v>
+        <v>84.24588971269188</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.541280000000015</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>72.34247620759962</v>
+        <v>68.22793169625137</v>
       </c>
       <c r="T10" t="n">
-        <v>72.34247620759962</v>
+        <v>68.22793169625137</v>
       </c>
     </row>
     <row r="11">
@@ -1242,10 +1242,10 @@
         <v>6.300000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P11" t="n">
-        <v>89.4481267198523</v>
+        <v>83.72198103033016</v>
       </c>
       <c r="Q11" t="n">
         <v>-4.745900000000006</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>70.46045776310058</v>
+        <v>66.34591325175234</v>
       </c>
       <c r="T11" t="n">
-        <v>70.46045776310058</v>
+        <v>66.34591325175234</v>
       </c>
     </row>
     <row r="12">
@@ -1316,10 +1316,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P12" t="n">
-        <v>78.96995307261801</v>
+        <v>73.24380738309587</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.438970000000012</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>65.51405096835529</v>
+        <v>61.39950645700704</v>
       </c>
       <c r="T12" t="n">
-        <v>65.51405096835529</v>
+        <v>61.39950645700704</v>
       </c>
     </row>
     <row r="13">
@@ -1390,10 +1390,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P13" t="n">
-        <v>78.09677193534849</v>
+        <v>72.37062624582634</v>
       </c>
       <c r="Q13" t="n">
         <v>2.970269999999999</v>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>67.95306802671098</v>
+        <v>63.83852351536274</v>
       </c>
       <c r="T13" t="n">
-        <v>67.95306802671098</v>
+        <v>63.83852351536274</v>
       </c>
     </row>
     <row r="14">
@@ -1464,10 +1464,10 @@
         <v>12.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P14" t="n">
-        <v>67.61859828811421</v>
+        <v>61.89245259859207</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.541280000000015</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>56.92406363285215</v>
+        <v>52.8095191215039</v>
       </c>
       <c r="T14" t="n">
-        <v>56.92406363285215</v>
+        <v>52.8095191215039</v>
       </c>
     </row>
     <row r="15">
@@ -1538,10 +1538,10 @@
         <v>13.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P15" t="n">
-        <v>63.25269260176658</v>
+        <v>57.52654691224444</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.541280000000015</v>
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>53.91265492684677</v>
+        <v>49.79811041549852</v>
       </c>
       <c r="T15" t="n">
-        <v>53.91265492684677</v>
+        <v>49.79811041549852</v>
       </c>
     </row>
     <row r="16">
@@ -1612,10 +1612,10 @@
         <v>20.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.001323189613366357</v>
       </c>
       <c r="P16" t="n">
-        <v>40.22301415569359</v>
+        <v>34.49305103571177</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.643590000000017</v>
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.0008858839633591573</v>
       </c>
       <c r="P42" t="n">
-        <v>128.2623500880567</v>
+        <v>114.1311750440284</v>
       </c>
       <c r="Q42" t="n">
         <v>-3.643590000000017</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>97.99311759000679</v>
+        <v>87.81723974528161</v>
       </c>
       <c r="T42" t="n">
-        <v>97.99311759000679</v>
+        <v>87.81723974528161</v>
       </c>
     </row>
     <row r="43">
@@ -3614,10 +3614,10 @@
         <v>0.15</v>
       </c>
       <c r="O43" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.0008858839633591573</v>
       </c>
       <c r="P43" t="n">
-        <v>127.9308878428104</v>
+        <v>113.799712798782</v>
       </c>
       <c r="Q43" t="n">
         <v>-2.541280000000015</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>98.52481428857013</v>
+        <v>88.34893644384495</v>
       </c>
       <c r="T43" t="n">
-        <v>98.52481428857013</v>
+        <v>88.34893644384495</v>
       </c>
     </row>
     <row r="44">
@@ -3688,10 +3688,10 @@
         <v>0.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.0008858839633591573</v>
       </c>
       <c r="P44" t="n">
-        <v>127.7099130126462</v>
+        <v>113.5787379686178</v>
       </c>
       <c r="Q44" t="n">
         <v>-2.541280000000015</v>
@@ -3700,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>98.37239562101954</v>
+        <v>88.19651777629436</v>
       </c>
       <c r="T44" t="n">
-        <v>98.37239562101954</v>
+        <v>88.19651777629436</v>
       </c>
     </row>
     <row r="45">
@@ -3762,10 +3762,10 @@
         <v>2.25</v>
       </c>
       <c r="O45" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.0008858839633591573</v>
       </c>
       <c r="P45" t="n">
-        <v>123.2904164093617</v>
+        <v>109.1592413653333</v>
       </c>
       <c r="Q45" t="n">
         <v>-2.541280000000015</v>
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>95.32402227000799</v>
+        <v>85.14814442528278</v>
       </c>
       <c r="T45" t="n">
-        <v>95.32402227000799</v>
+        <v>85.14814442528278</v>
       </c>
     </row>
     <row r="46">
@@ -3836,10 +3836,10 @@
         <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.0008858839633591573</v>
       </c>
       <c r="P46" t="n">
-        <v>122.7379793339511</v>
+        <v>108.6068042899228</v>
       </c>
       <c r="Q46" t="n">
         <v>-2.541280000000015</v>
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>94.94297560113154</v>
+        <v>84.76709775640636</v>
       </c>
       <c r="T46" t="n">
-        <v>94.94297560113154</v>
+        <v>84.76709775640636</v>
       </c>
     </row>
     <row r="47">
@@ -3910,10 +3910,10 @@
         <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.0008858839633591573</v>
       </c>
       <c r="P47" t="n">
-        <v>120.5282310323089</v>
+        <v>106.3970559882806</v>
       </c>
       <c r="Q47" t="n">
         <v>4.072579999999988</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>97.98073712496091</v>
+        <v>87.80485928023573</v>
       </c>
       <c r="T47" t="n">
-        <v>97.98073712496091</v>
+        <v>87.80485928023573</v>
       </c>
     </row>
     <row r="48">
@@ -3984,10 +3984,10 @@
         <v>4.25</v>
       </c>
       <c r="O48" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.0008858839633591573</v>
       </c>
       <c r="P48" t="n">
-        <v>118.8709198060772</v>
+        <v>104.7397447620489</v>
       </c>
       <c r="Q48" t="n">
         <v>-2.541280000000015</v>
@@ -3996,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>92.27564891899641</v>
+        <v>82.09977107427123</v>
       </c>
       <c r="T48" t="n">
-        <v>92.27564891899641</v>
+        <v>82.09977107427123</v>
       </c>
     </row>
     <row r="49">
@@ -4058,10 +4058,10 @@
         <v>4.28</v>
       </c>
       <c r="O49" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.0008858839633591573</v>
       </c>
       <c r="P49" t="n">
-        <v>118.804627357028</v>
+        <v>104.6734523129996</v>
       </c>
       <c r="Q49" t="n">
         <v>-3.643590000000017</v>
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>91.46959861884204</v>
+        <v>81.29372077411686</v>
       </c>
       <c r="T49" t="n">
-        <v>91.46959861884204</v>
+        <v>81.29372077411686</v>
       </c>
     </row>
     <row r="50">
@@ -4132,10 +4132,10 @@
         <v>5.78</v>
       </c>
       <c r="O50" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.0008858839633591573</v>
       </c>
       <c r="P50" t="n">
-        <v>115.4900049045646</v>
+        <v>101.3588298605363</v>
       </c>
       <c r="Q50" t="n">
         <v>-2.541280000000015</v>
@@ -4144,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>89.94364330547256</v>
+        <v>79.76776546074738</v>
       </c>
       <c r="T50" t="n">
-        <v>89.94364330547256</v>
+        <v>79.76776546074738</v>
       </c>
     </row>
     <row r="51">
@@ -4206,10 +4206,10 @@
         <v>8.780000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.0008858839633591573</v>
       </c>
       <c r="P51" t="n">
-        <v>108.8607599996379</v>
+        <v>94.7295849556096</v>
       </c>
       <c r="Q51" t="n">
         <v>-0.3366600000000091</v>
@@ -4218,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>86.8917326787336</v>
+        <v>76.7158548340084</v>
       </c>
       <c r="T51" t="n">
-        <v>86.8917326787336</v>
+        <v>76.7158548340084</v>
       </c>
     </row>
     <row r="52">
@@ -4280,10 +4280,10 @@
         <v>11.28</v>
       </c>
       <c r="O52" t="n">
-        <v>0.001596431204997816</v>
+        <v>0.0008858839633591573</v>
       </c>
       <c r="P52" t="n">
-        <v>103.3363892455324</v>
+        <v>89.20521420150403</v>
       </c>
       <c r="Q52" t="n">
         <v>1.867959999999982</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>84.60191538974752</v>
+        <v>74.42603754502234</v>
       </c>
       <c r="T52" t="n">
-        <v>84.60191538974752</v>
+        <v>74.42603754502234</v>
       </c>
     </row>
   </sheetData>
